--- a/Template_Without_VBA/TemplateWithoutVBA.xlsx
+++ b/Template_Without_VBA/TemplateWithoutVBA.xlsx
@@ -5,15 +5,15 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SAPDevelop\Excel_Templates\Template_Without_VBA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\I519576\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5540184A-07F1-4C81-9ED2-CAD176FFA494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37241434-039C-4692-AA01-DF631EA1AD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="12645" tabRatio="374" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="374" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="SAP IBP Formatting Sheet" sheetId="14" state="hidden" r:id="rId1"/>
+    <sheet name="SAP IBP Formatting Sheet" sheetId="15" state="hidden" r:id="rId1"/>
     <sheet name="Planning View 1" sheetId="5" r:id="rId2"/>
     <sheet name="Planning View 2" sheetId="7" r:id="rId3"/>
   </sheets>
@@ -158,12 +158,13 @@
     <definedName name="SOP_Heading8" localSheetId="2">" "</definedName>
     <definedName name="SOP_Heading9" localSheetId="1">" "</definedName>
     <definedName name="SOP_Heading9" localSheetId="2">" "</definedName>
+    <definedName name="SOP_Planning_Area" localSheetId="0">"PLAIBP1"</definedName>
     <definedName name="SOP_Planning_Area">"Planning area"</definedName>
-    <definedName name="SOP_Planning_Scope" localSheetId="0">"No Subnetwork selected | Base Version | Baseline"</definedName>
+    <definedName name="SOP_Planning_Scope" localSheetId="0">"No Subnetwork ID selected | Base Version | Baseline"</definedName>
     <definedName name="SOP_Planning_Scope">" "</definedName>
-    <definedName name="SOP_Planning_Scope_v2" localSheetId="0">"CW43 M10 2024 - CW43 M10 2026 | Base Version | Baseline"</definedName>
+    <definedName name="SOP_Planning_Scope_v2" localSheetId="0">"CW51 M12 2025 - CW50 M12 2027 | Base Version | Baseline"</definedName>
     <definedName name="SOP_Planning_Scope_v2">"CW13 M3 2023 - CW46 M11 2023 | Base Version | Baseline | My Product Groups"</definedName>
-    <definedName name="SOP_Refresh_Timestamp" localSheetId="0">45590.7909490741</definedName>
+    <definedName name="SOP_Refresh_Timestamp" localSheetId="0">46008.666875</definedName>
     <definedName name="SOP_Refresh_Timestamp">0</definedName>
     <definedName name="SOP_Template_Name">" "</definedName>
     <definedName name="SOP_WB_Filter" localSheetId="0">{" "}</definedName>
@@ -175,6 +176,9 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -182,6 +186,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -192,9 +198,10 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Votteler, Julia</author>
+    <author>Juhasz, Tibor Gergely</author>
   </authors>
   <commentList>
-    <comment ref="D40" authorId="0" shapeId="0" xr:uid="{6EA09104-38BF-4FC5-8DC7-F349D8592355}">
+    <comment ref="D40" authorId="0" shapeId="0" xr:uid="{D39659DB-7ED7-4574-8DEC-BF9C42833DAB}">
       <text>
         <r>
           <rPr>
@@ -207,7 +214,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D43" authorId="0" shapeId="0" xr:uid="{18C03B9B-40E7-4224-9A09-D63C174850BA}">
+    <comment ref="D43" authorId="0" shapeId="0" xr:uid="{3D106929-C9D6-4BE3-8EFE-D7200B5DA2B1}">
       <text>
         <r>
           <rPr>
@@ -220,7 +227,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D64" authorId="0" shapeId="0" xr:uid="{247FDBAD-7A46-4587-AAAD-E2750444B10D}">
+    <comment ref="D64" authorId="1" shapeId="0" xr:uid="{B7A0D376-75A1-4E02-8322-DA8D1D1882D0}">
       <text>
         <r>
           <rPr>
@@ -229,11 +236,11 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Property#PERIODID#TIMELEVEL#Equals#TOTAL</t>
+          <t>TotalMember</t>
         </r>
       </text>
     </comment>
-    <comment ref="D67" authorId="0" shapeId="0" xr:uid="{8F14B7D3-3DF9-455E-BEBC-73BD9369602A}">
+    <comment ref="D67" authorId="0" shapeId="0" xr:uid="{16AE673D-F821-44AF-AF89-60AD2958BA7F}">
       <text>
         <r>
           <rPr>
@@ -273,9 +280,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="37">
+  <si>
+    <t>SAP IBP Formatting Sheet</t>
+  </si>
   <si>
     <t>Version_1_1</t>
+  </si>
+  <si>
+    <t>Note: If there are conflicts, the format settings in the lower sections override the ones in the upper section.</t>
   </si>
   <si>
     <t>Default Formatting</t>
@@ -288,6 +301,12 @@
   </si>
   <si>
     <t>Column</t>
+  </si>
+  <si>
+    <t>In the cells with the text "10,000" (“Data” column) and "Label" ("Header" columns), you can define the format you want to have in the planning view using the standard Microsoft Excel cell formatting functions._x000D_
+For a better overview of the formatting settings, you can right-click the cell and choose "Format Cells…"._x000D_
+By default, all the formatting settings that have been defined are applied and "All" is displayed in the "Use" column._x000D_
+You can further specify which settings (properties) of the defined format you want to be taken over in the planning view. To do so, double-click in a "Use" cell. In the dialog that opens, select the properties you want to use.</t>
   </si>
   <si>
     <t>Data</t>
@@ -314,7 +333,13 @@
     <t>Row</t>
   </si>
   <si>
+    <t>Member/Property Formatting</t>
+  </si>
+  <si>
     <t>Priority to Row or Column</t>
+  </si>
+  <si>
+    <t>You can decide if you want the row or the column formatting to overwrite the other by choosing either "Priority to Column Format" or "Priority to Row Format" under the header of each section. With these options, you can specify whether the formats defined for rows or columns are applied first. For example, when you choose "Priority to Row Format", the "Column" section is displayed first in the formatting section, and the "Row" section is displayed in second position. As the lower rules overwrite the preceding rules, the formatting you define for the "Row" section is used in the planning view if there are conflicts.</t>
   </si>
   <si>
     <t>Default Format for Non-Editable Cells</t>
@@ -326,6 +351,15 @@
     <t>Pattern</t>
   </si>
   <si>
+    <t>Default Format for Cells Containing SAP IBP Formulas</t>
+  </si>
+  <si>
+    <t>Default Format for Changed Cells</t>
+  </si>
+  <si>
+    <t>Border | FontColorIndex</t>
+  </si>
+  <si>
     <t>Formatting on Specific Member/Property:</t>
   </si>
   <si>
@@ -333,6 +367,18 @@
   </si>
   <si>
     <t>FontBold</t>
+  </si>
+  <si>
+    <t>Key Figures.Percentage = Y</t>
+  </si>
+  <si>
+    <t>NumberFormat</t>
+  </si>
+  <si>
+    <t>Day.RELATIVE = 0 OR Week (technical).RELATIVE = 0 OR Week.RELATIVE = 0 OR Month.RELATIVE = 0 OR Quarter.RELATIVE = 0 OR Year.RELATIVE = 0</t>
+  </si>
+  <si>
+    <t>FontStyle</t>
   </si>
   <si>
     <t>Row and Column Banding</t>
@@ -349,48 +395,6 @@
   <si>
     <t>Start here--&gt;</t>
   </si>
-  <si>
-    <t>SAP IBP Formatting Sheet</t>
-  </si>
-  <si>
-    <t>Border | FontColorIndex</t>
-  </si>
-  <si>
-    <t>NumberFormat</t>
-  </si>
-  <si>
-    <t>FontStyle</t>
-  </si>
-  <si>
-    <t>Note: If there are conflicts, the format settings in the lower sections override the ones in the upper section.</t>
-  </si>
-  <si>
-    <t>Member/Property Formatting</t>
-  </si>
-  <si>
-    <t>Default Format for Changed Cells</t>
-  </si>
-  <si>
-    <t>Key Figures.Percentage = Y</t>
-  </si>
-  <si>
-    <t>Mixed Time.Time Level = TOTAL</t>
-  </si>
-  <si>
-    <t>Day.RELATIVE = 0 OR Week (technical).RELATIVE = 0 OR Week.RELATIVE = 0 OR Month.RELATIVE = 0 OR Quarter.RELATIVE = 0 OR Year.RELATIVE = 0</t>
-  </si>
-  <si>
-    <t>In the cells with the text "10,000" (“Data” column) and "Label" ("Header" columns), you can define the format you want to have in the planning view using the standard Microsoft Excel cell formatting functions._x000D_
-For a better overview of the formatting settings, you can right-click the cell and choose "Format Cells…"._x000D_
-By default, all the formatting settings that have been defined are applied and "All" is displayed in the "Use" column._x000D_
-You can further specify which settings (properties) of the defined format you want to be taken over in the planning view. To do so, double-click in a "Use" cell. In the dialog that opens, select the properties you want to use.</t>
-  </si>
-  <si>
-    <t>You can decide if you want the row or the column formatting to overwrite the other by choosing either "Priority to Column Format" or "Priority to Row Format" under the header of each section. With these options, you can specify whether the formats defined for rows or columns are applied first. For example, when you choose "Priority to Row Format", the "Column" section is displayed first in the formatting section, and the "Row" section is displayed in second position. As the lower rules overwrite the preceding rules, the formatting you define for the "Row" section is used in the planning view if there are conflicts.</t>
-  </si>
-  <si>
-    <t>Default Format for Cells Containing SAP IBP Formulas</t>
-  </si>
 </sst>
 </file>
 
@@ -399,7 +403,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -470,20 +474,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="10"/>
       <color theme="1"/>
@@ -526,7 +516,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -534,18 +523,35 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="1" tint="0.34998626667073579"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF21A3F1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -554,7 +560,6 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
@@ -571,7 +576,7 @@
       <charset val="238"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -586,12 +591,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF404040"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD3D3D3"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -600,11 +599,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
       </patternFill>
     </fill>
     <fill>
@@ -626,7 +620,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -778,69 +772,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -980,17 +911,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -1030,13 +950,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1045,7 +1001,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1063,32 +1019,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="1" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="1" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1102,22 +1058,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1130,72 +1080,72 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="20" fillId="7" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1203,20 +1153,20 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1224,15 +1174,15 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1240,13 +1190,13 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1255,57 +1205,49 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="5"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="5"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="5"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Accent6" xfId="1" builtinId="49"/>
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF21A3F1"/>
+      <color rgb="FF464646"/>
       <color rgb="FF2965AD"/>
       <color rgb="FF3178CD"/>
       <color rgb="FF4F8CD5"/>
@@ -1314,8 +1256,6 @@
       <color rgb="FFC5D9F1"/>
       <color rgb="FF003283"/>
       <color rgb="FF970A82"/>
-      <color rgb="FFFF9124"/>
-      <color rgb="FF21A3F1"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1505,6 +1445,18 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp44.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
@@ -1544,13 +1496,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24577" name="cbApplyLevelFormatting" hidden="1">
+            <xdr:cNvPr id="27649" name="cbApplyLevelFormatting" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24577"/>
+                  <a14:compatExt spid="_x0000_s27649"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000016C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1605,19 +1557,19 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>2724150</xdr:colOff>
+          <xdr:colOff>2733675</xdr:colOff>
           <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24578" name="Group Box 2" hidden="1">
+            <xdr:cNvPr id="27650" name="Group Box 2" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24578"/>
+                  <a14:compatExt spid="_x0000_s27650"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000026C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1687,13 +1639,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24579" name="obLevelRowFirst" hidden="1">
+            <xdr:cNvPr id="27651" name="obLevelRowFirst" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24579"/>
+                  <a14:compatExt spid="_x0000_s27651"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000036C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1767,19 +1719,19 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
+          <xdr:colOff>390525</xdr:colOff>
           <xdr:row>5</xdr:row>
           <xdr:rowOff>295275</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24580" name="obLevelColumnFirst" hidden="1">
+            <xdr:cNvPr id="27652" name="obLevelColumnFirst" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24580"/>
+                  <a14:compatExt spid="_x0000_s27652"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000046C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1852,20 +1804,20 @@
           <xdr:rowOff>9525</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1057275</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>17</xdr:row>
           <xdr:rowOff>47625</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24581" name="cbUseDefaultLevelFirst" hidden="1">
+            <xdr:cNvPr id="27653" name="cbUseDefaultLevelFirst" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24581"/>
+                  <a14:compatExt spid="_x0000_s27653"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000056C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1938,20 +1890,20 @@
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1057275</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>11</xdr:row>
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24582" name="cbUseDefaultLevelSecond" hidden="1">
+            <xdr:cNvPr id="27654" name="cbUseDefaultLevelSecond" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24582"/>
+                  <a14:compatExt spid="_x0000_s27654"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000066C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2031,13 +1983,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24583" name="cbApplyMemberFormatting" hidden="1">
+            <xdr:cNvPr id="27655" name="cbApplyMemberFormatting" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24583"/>
+                  <a14:compatExt spid="_x0000_s27655"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000076C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2092,19 +2044,19 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>12</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
+          <xdr:colOff>28575</xdr:colOff>
           <xdr:row>22</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
+          <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24584" name="Group Box 8" hidden="1">
+            <xdr:cNvPr id="27656" name="Group Box 8" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24584"/>
+                  <a14:compatExt spid="_x0000_s27656"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000086C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2174,13 +2126,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24585" name="obMemberRowFirst" hidden="1">
+            <xdr:cNvPr id="27657" name="obMemberRowFirst" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24585"/>
+                  <a14:compatExt spid="_x0000_s27657"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000096C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2254,19 +2206,19 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
+          <xdr:colOff>390525</xdr:colOff>
           <xdr:row>21</xdr:row>
           <xdr:rowOff>295275</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24586" name="obMemberColumnFirst" hidden="1">
+            <xdr:cNvPr id="27658" name="obMemberColumnFirst" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24586"/>
+                  <a14:compatExt spid="_x0000_s27658"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A6C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2339,20 +2291,20 @@
           <xdr:rowOff>209550</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1057275</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>26</xdr:row>
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24587" name="cbApplyCalculatedMemberFirst" hidden="1">
+            <xdr:cNvPr id="27659" name="cbApplyCalculatedMemberFirst" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24587"/>
+                  <a14:compatExt spid="_x0000_s27659"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B6C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2425,20 +2377,20 @@
           <xdr:rowOff>57150</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1057275</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>29</xdr:row>
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24588" name="cbApplyImputableMemberFirst" hidden="1">
+            <xdr:cNvPr id="27660" name="cbApplyImputableMemberFirst" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24588"/>
+                  <a14:compatExt spid="_x0000_s27660"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C6C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2511,20 +2463,20 @@
           <xdr:rowOff>57150</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1057275</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>32</xdr:row>
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24589" name="cbApplyLocalMemberFirst" hidden="1">
+            <xdr:cNvPr id="27661" name="cbApplyLocalMemberFirst" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24589"/>
+                  <a14:compatExt spid="_x0000_s27661"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D6C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2597,20 +2549,20 @@
           <xdr:rowOff>57150</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1057275</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>35</xdr:row>
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24590" name="cbApplyChangedMemberFirst" hidden="1">
+            <xdr:cNvPr id="27662" name="cbApplyChangedMemberFirst" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24590"/>
+                  <a14:compatExt spid="_x0000_s27662"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E6C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2683,20 +2635,20 @@
           <xdr:rowOff>47625</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1057275</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>38</xdr:row>
           <xdr:rowOff>9525</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24591" name="cbApplySpecificMemberFirst" hidden="1">
+            <xdr:cNvPr id="27663" name="cbApplySpecificMemberFirst" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24591"/>
+                  <a14:compatExt spid="_x0000_s27663"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F6C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2776,13 +2728,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24592" name="AddMemberFirst" hidden="1">
+            <xdr:cNvPr id="27664" name="AddMemberFirst" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24592"/>
+                  <a14:compatExt spid="_x0000_s27664"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000106C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2839,20 +2791,20 @@
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1057275</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>50</xdr:row>
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24593" name="cbApplyCalculatedMemberSecond" hidden="1">
+            <xdr:cNvPr id="27665" name="cbApplyCalculatedMemberSecond" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24593"/>
+                  <a14:compatExt spid="_x0000_s27665"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000116C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2925,20 +2877,20 @@
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1057275</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>53</xdr:row>
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24594" name="cbApplyImputableMemberSecond" hidden="1">
+            <xdr:cNvPr id="27666" name="cbApplyImputableMemberSecond" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24594"/>
+                  <a14:compatExt spid="_x0000_s27666"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000126C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3011,20 +2963,20 @@
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1057275</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>56</xdr:row>
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24595" name="cbApplyLocalMemberSecond" hidden="1">
+            <xdr:cNvPr id="27667" name="cbApplyLocalMemberSecond" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24595"/>
+                  <a14:compatExt spid="_x0000_s27667"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000136C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3097,20 +3049,20 @@
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1057275</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>59</xdr:row>
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24596" name="cbApplyChangedMemberSecond" hidden="1">
+            <xdr:cNvPr id="27668" name="cbApplyChangedMemberSecond" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24596"/>
+                  <a14:compatExt spid="_x0000_s27668"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000146C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3183,20 +3135,20 @@
           <xdr:rowOff>47625</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1057275</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>62</xdr:row>
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24597" name="cbApplySpecificMemberSecond" hidden="1">
+            <xdr:cNvPr id="27669" name="cbApplySpecificMemberSecond" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24597"/>
+                  <a14:compatExt spid="_x0000_s27669"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000156C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3276,13 +3228,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24598" name="AddMemberSecond" hidden="1">
+            <xdr:cNvPr id="27670" name="AddMemberSecond" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24598"/>
+                  <a14:compatExt spid="_x0000_s27670"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000166C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3346,13 +3298,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24599" name="cbApplyOddEvenFormatting" hidden="1">
+            <xdr:cNvPr id="27671" name="cbApplyOddEvenFormatting" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24599"/>
+                  <a14:compatExt spid="_x0000_s27671"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000176C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3407,19 +3359,19 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>12</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
+          <xdr:colOff>28575</xdr:colOff>
           <xdr:row>74</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24600" name="Group Box 24" hidden="1">
+            <xdr:cNvPr id="27672" name="Group Box 24" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24600"/>
+                  <a14:compatExt spid="_x0000_s27672"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000186C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3489,13 +3441,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24601" name="obOddEvenRowFirst" hidden="1">
+            <xdr:cNvPr id="27673" name="obOddEvenRowFirst" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24601"/>
+                  <a14:compatExt spid="_x0000_s27673"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000196C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3569,19 +3521,19 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
+          <xdr:colOff>390525</xdr:colOff>
           <xdr:row>73</xdr:row>
           <xdr:rowOff>276225</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24602" name="obOddEvenColumnFirst" hidden="1">
+            <xdr:cNvPr id="27674" name="obOddEvenColumnFirst" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24602"/>
+                  <a14:compatExt spid="_x0000_s27674"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A6C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3654,20 +3606,20 @@
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1057275</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>78</xdr:row>
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24603" name="cbUseOddFirst" hidden="1">
+            <xdr:cNvPr id="27675" name="cbUseOddFirst" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24603"/>
+                  <a14:compatExt spid="_x0000_s27675"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B6C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3740,20 +3692,20 @@
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1057275</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>81</xdr:row>
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24604" name="cbUseEvenFirst" hidden="1">
+            <xdr:cNvPr id="27676" name="cbUseEvenFirst" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24604"/>
+                  <a14:compatExt spid="_x0000_s27676"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001C6C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3826,20 +3778,20 @@
           <xdr:rowOff>9525</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1057275</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>86</xdr:row>
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24605" name="cbUseOddSecond" hidden="1">
+            <xdr:cNvPr id="27677" name="cbUseOddSecond" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24605"/>
+                  <a14:compatExt spid="_x0000_s27677"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001D6C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3912,20 +3864,20 @@
           <xdr:rowOff>9525</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>2</xdr:col>
-          <xdr:colOff>1057275</xdr:colOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>89</xdr:row>
           <xdr:rowOff>38100</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24606" name="cbUseEvenSecond" hidden="1">
+            <xdr:cNvPr id="27678" name="cbUseEvenSecond" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24606"/>
+                  <a14:compatExt spid="_x0000_s27678"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E6C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4005,13 +3957,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24607" name="AddedMember1_1" hidden="1">
+            <xdr:cNvPr id="27679" name="AddedMember1_1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24607"/>
+                  <a14:compatExt spid="_x0000_s27679"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F6C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4075,13 +4027,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24608" name="ChangeMember1_1" hidden="1">
+            <xdr:cNvPr id="27680" name="ChangeMember1_1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24608"/>
+                  <a14:compatExt spid="_x0000_s27680"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000206C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4145,13 +4097,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24609" name="UpMember1_1" hidden="1">
+            <xdr:cNvPr id="27681" name="UpMember1_1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24609"/>
+                  <a14:compatExt spid="_x0000_s27681"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000216C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4215,13 +4167,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24610" name="DownMember1_1" hidden="1">
+            <xdr:cNvPr id="27682" name="DownMember1_1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24610"/>
+                  <a14:compatExt spid="_x0000_s27682"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000226C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4285,13 +4237,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24611" name="AddedMember1_2" hidden="1">
+            <xdr:cNvPr id="27683" name="AddedMember1_2" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24611"/>
+                  <a14:compatExt spid="_x0000_s27683"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000236C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4355,13 +4307,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24612" name="ChangeMember1_2" hidden="1">
+            <xdr:cNvPr id="27684" name="ChangeMember1_2" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24612"/>
+                  <a14:compatExt spid="_x0000_s27684"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000024600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000246C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4425,13 +4377,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24613" name="UpMember1_2" hidden="1">
+            <xdr:cNvPr id="27685" name="UpMember1_2" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24613"/>
+                  <a14:compatExt spid="_x0000_s27685"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000025600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000256C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4495,13 +4447,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24614" name="DownMember1_2" hidden="1">
+            <xdr:cNvPr id="27686" name="DownMember1_2" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24614"/>
+                  <a14:compatExt spid="_x0000_s27686"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000026600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000266C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4565,13 +4517,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24615" name="AddedMember2_1" hidden="1">
+            <xdr:cNvPr id="27687" name="AddedMember2_1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24615"/>
+                  <a14:compatExt spid="_x0000_s27687"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000276C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4635,13 +4587,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24616" name="ChangeMember2_1" hidden="1">
+            <xdr:cNvPr id="27688" name="ChangeMember2_1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24616"/>
+                  <a14:compatExt spid="_x0000_s27688"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000286C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4705,13 +4657,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24617" name="UpMember2_1" hidden="1">
+            <xdr:cNvPr id="27689" name="UpMember2_1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24617"/>
+                  <a14:compatExt spid="_x0000_s27689"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000029600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000296C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4775,13 +4727,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24618" name="DownMember2_1" hidden="1">
+            <xdr:cNvPr id="27690" name="DownMember2_1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24618"/>
+                  <a14:compatExt spid="_x0000_s27690"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A6C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4845,13 +4797,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24619" name="AddedMember2_2" hidden="1">
+            <xdr:cNvPr id="27691" name="AddedMember2_2" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24619"/>
+                  <a14:compatExt spid="_x0000_s27691"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B6C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4915,13 +4867,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24620" name="ChangeMember2_2" hidden="1">
+            <xdr:cNvPr id="27692" name="ChangeMember2_2" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24620"/>
+                  <a14:compatExt spid="_x0000_s27692"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C6C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4985,13 +4937,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24621" name="UpMember2_2" hidden="1">
+            <xdr:cNvPr id="27693" name="UpMember2_2" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24621"/>
+                  <a14:compatExt spid="_x0000_s27693"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D6C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5055,13 +5007,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="24622" name="DownMember2_2" hidden="1">
+            <xdr:cNvPr id="27694" name="DownMember2_2" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s24622"/>
+                  <a14:compatExt spid="_x0000_s27694"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E600000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E6C0000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5104,6 +5056,264 @@
           </xdr:txBody>
         </xdr:sp>
         <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>266700</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>57150</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="27695" name="cbApplyLevelFormattingShape" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s27695"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F6C0000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Apply</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>266700</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>66675</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>57150</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="27696" name="cbApplyMemberFormattingShape" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s27696"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000306C0000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Apply</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>266700</xdr:colOff>
+          <xdr:row>72</xdr:row>
+          <xdr:rowOff>57150</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>57150</xdr:colOff>
+          <xdr:row>72</xdr:row>
+          <xdr:rowOff>333375</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="27697" name="cbApplyOddEvenFormattingShape" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s27697"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-0000316C0000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="18288" rIns="0" bIns="18288" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Apply</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
       </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
@@ -5677,7 +5887,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE2E9263-B567-4B32-A171-A65AC2A7FEB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDDA7BC4-37E1-4B79-8E7D-DCD1166F0607}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:Q146"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -5703,23 +5913,23 @@
   <sheetData>
     <row r="1" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
-      <c r="B1" s="56" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
+      <c r="B1" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
     </row>
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32" t="s">
-        <v>0</v>
+      <c r="A2" s="28" t="s">
+        <v>1</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5736,7 +5946,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="3" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -5763,46 +5973,46 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:17" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="28.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="58"/>
-      <c r="L5" s="59"/>
+      <c r="B5" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="55"/>
       <c r="Q5" s="19" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="28.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="62"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="58"/>
       <c r="Q6" s="20" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
-      <c r="B7" s="63" t="s">
-        <v>4</v>
+      <c r="B7" s="59" t="s">
+        <v>6</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
@@ -5814,13 +6024,13 @@
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
       <c r="L7" s="16"/>
-      <c r="Q7" s="66" t="s">
-        <v>35</v>
+      <c r="Q7" s="62" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
-      <c r="B8" s="64"/>
+      <c r="B8" s="60"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -5831,75 +6041,75 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="10"/>
-      <c r="Q8" s="66"/>
+      <c r="Q8" s="62"/>
     </row>
     <row r="9" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
-      <c r="B9" s="64"/>
+      <c r="B9" s="60"/>
       <c r="C9" s="5"/>
       <c r="D9" s="6"/>
-      <c r="E9" s="67" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="68"/>
-      <c r="G9" s="69"/>
+      <c r="E9" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="64"/>
+      <c r="G9" s="65"/>
       <c r="H9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="67" t="s">
-        <v>7</v>
-      </c>
-      <c r="J9" s="68"/>
-      <c r="K9" s="69"/>
+        <v>9</v>
+      </c>
+      <c r="I9" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="64"/>
+      <c r="K9" s="65"/>
       <c r="L9" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q9" s="66"/>
+        <v>9</v>
+      </c>
+      <c r="Q9" s="62"/>
     </row>
     <row r="10" spans="1:17" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="70"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="66"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
       <c r="H10" s="8"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="34"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
       <c r="L10" s="10"/>
-      <c r="Q10" s="66"/>
+      <c r="Q10" s="62"/>
     </row>
     <row r="11" spans="1:17" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="35" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="36">
+      <c r="B11" s="60"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="30"/>
+      <c r="F11" s="41">
         <v>10000</v>
       </c>
-      <c r="G11" s="34"/>
-      <c r="H11" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="34"/>
-      <c r="J11" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="K11" s="34"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="30"/>
+      <c r="J11" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="30"/>
       <c r="L11" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q11" s="66"/>
+        <v>14</v>
+      </c>
+      <c r="Q11" s="62"/>
     </row>
     <row r="12" spans="1:17" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
-      <c r="B12" s="65"/>
-      <c r="C12" s="72"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="68"/>
       <c r="D12" s="13"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
@@ -5909,12 +6119,12 @@
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
       <c r="L12" s="14"/>
-      <c r="Q12" s="66"/>
+      <c r="Q12" s="62"/>
     </row>
     <row r="13" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
-      <c r="B13" s="73" t="s">
-        <v>12</v>
+      <c r="B13" s="69" t="s">
+        <v>15</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -5926,11 +6136,11 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="10"/>
-      <c r="Q13" s="66"/>
+      <c r="Q13" s="62"/>
     </row>
     <row r="14" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
-      <c r="B14" s="64"/>
+      <c r="B14" s="60"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -5941,75 +6151,75 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="10"/>
-      <c r="Q14" s="66"/>
+      <c r="Q14" s="62"/>
     </row>
     <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
-      <c r="B15" s="64"/>
+      <c r="B15" s="60"/>
       <c r="C15" s="5"/>
       <c r="D15" s="6"/>
-      <c r="E15" s="67" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="68"/>
-      <c r="G15" s="69"/>
+      <c r="E15" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="64"/>
+      <c r="G15" s="65"/>
       <c r="H15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I15" s="67" t="s">
-        <v>7</v>
-      </c>
-      <c r="J15" s="68"/>
-      <c r="K15" s="69"/>
+        <v>9</v>
+      </c>
+      <c r="I15" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="64"/>
+      <c r="K15" s="65"/>
       <c r="L15" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q15" s="66"/>
+        <v>9</v>
+      </c>
+      <c r="Q15" s="62"/>
     </row>
     <row r="16" spans="1:17" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
-      <c r="B16" s="64"/>
-      <c r="C16" s="70"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="66"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
       <c r="H16" s="8"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
       <c r="L16" s="10"/>
-      <c r="Q16" s="66"/>
+      <c r="Q16" s="62"/>
     </row>
     <row r="17" spans="1:17" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
-      <c r="B17" s="64"/>
-      <c r="C17" s="71"/>
-      <c r="D17" s="35" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="36">
+      <c r="B17" s="60"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="30"/>
+      <c r="F17" s="41">
         <v>10000</v>
       </c>
-      <c r="G17" s="34"/>
-      <c r="H17" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="I17" s="34"/>
-      <c r="J17" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="K17" s="34"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="30"/>
+      <c r="J17" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="30"/>
       <c r="L17" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q17" s="66"/>
+        <v>14</v>
+      </c>
+      <c r="Q17" s="62"/>
     </row>
     <row r="18" spans="1:17" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="72"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="68"/>
       <c r="D18" s="13"/>
       <c r="E18" s="18"/>
       <c r="F18" s="18"/>
@@ -6019,7 +6229,7 @@
       <c r="J18" s="18"/>
       <c r="K18" s="18"/>
       <c r="L18" s="14"/>
-      <c r="Q18" s="66"/>
+      <c r="Q18" s="62"/>
     </row>
     <row r="19" spans="1:17" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
@@ -6034,7 +6244,7 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
-      <c r="Q19" s="66"/>
+      <c r="Q19" s="62"/>
     </row>
     <row r="20" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
@@ -6051,46 +6261,46 @@
       <c r="L20" s="2"/>
       <c r="Q20" s="21"/>
     </row>
-    <row r="21" spans="1:17" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" ht="28.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
-      <c r="B21" s="74" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="75"/>
-      <c r="D21" s="75"/>
-      <c r="E21" s="75"/>
-      <c r="F21" s="75"/>
-      <c r="G21" s="75"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="75"/>
-      <c r="J21" s="75"/>
-      <c r="K21" s="75"/>
-      <c r="L21" s="76"/>
+      <c r="B21" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="55"/>
       <c r="Q21" s="22" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
-      <c r="B22" s="77"/>
-      <c r="C22" s="78"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="78"/>
-      <c r="G22" s="78"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="78"/>
-      <c r="L22" s="79"/>
-      <c r="Q22" s="66" t="s">
-        <v>36</v>
+      <c r="B22" s="70"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="71"/>
+      <c r="L22" s="72"/>
+      <c r="Q22" s="62" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
-      <c r="B23" s="73" t="s">
-        <v>12</v>
+      <c r="B23" s="69" t="s">
+        <v>15</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -6102,76 +6312,76 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="10"/>
-      <c r="Q23" s="66"/>
+      <c r="Q23" s="62"/>
     </row>
     <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
-      <c r="B24" s="64"/>
+      <c r="B24" s="60"/>
       <c r="C24" s="5"/>
       <c r="D24" s="6"/>
-      <c r="E24" s="67" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="68"/>
-      <c r="G24" s="69"/>
+      <c r="E24" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="64"/>
+      <c r="G24" s="65"/>
       <c r="H24" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I24" s="67" t="s">
-        <v>7</v>
-      </c>
-      <c r="J24" s="68"/>
-      <c r="K24" s="69"/>
+        <v>9</v>
+      </c>
+      <c r="I24" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="64"/>
+      <c r="K24" s="65"/>
       <c r="L24" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q24" s="66"/>
+        <v>9</v>
+      </c>
+      <c r="Q24" s="62"/>
     </row>
     <row r="25" spans="1:17" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
-      <c r="B25" s="64"/>
-      <c r="C25" s="70"/>
+      <c r="B25" s="60"/>
+      <c r="C25" s="66"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
       <c r="H25" s="8"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="34"/>
-      <c r="K25" s="34"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
       <c r="L25" s="10"/>
-      <c r="Q25" s="66"/>
+      <c r="Q25" s="62"/>
     </row>
     <row r="26" spans="1:17" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
-      <c r="B26" s="64"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="35" t="s">
+      <c r="B26" s="60"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="30"/>
+      <c r="F26" s="44">
+        <v>10000</v>
+      </c>
+      <c r="G26" s="30"/>
+      <c r="H26" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="34"/>
-      <c r="F26" s="48">
-        <v>10000</v>
-      </c>
-      <c r="G26" s="34"/>
-      <c r="H26" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="I26" s="34"/>
-      <c r="J26" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="K26" s="34"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="K26" s="30"/>
       <c r="L26" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q26" s="66"/>
+        <v>14</v>
+      </c>
+      <c r="Q26" s="62"/>
     </row>
     <row r="27" spans="1:17" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
-      <c r="B27" s="64"/>
-      <c r="C27" s="80"/>
-      <c r="D27" s="52"/>
+      <c r="B27" s="60"/>
+      <c r="C27" s="73"/>
+      <c r="D27" s="37"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
@@ -6179,54 +6389,54 @@
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
-      <c r="L27" s="53"/>
-      <c r="Q27" s="66"/>
+      <c r="L27" s="38"/>
+      <c r="Q27" s="62"/>
     </row>
     <row r="28" spans="1:17" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
-      <c r="B28" s="64"/>
-      <c r="C28" s="71"/>
+      <c r="B28" s="60"/>
+      <c r="C28" s="67"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
       <c r="L28" s="10"/>
-      <c r="Q28" s="66"/>
+      <c r="Q28" s="62"/>
     </row>
     <row r="29" spans="1:17" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
-      <c r="B29" s="64"/>
-      <c r="C29" s="71"/>
-      <c r="D29" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" s="34"/>
-      <c r="F29" s="39">
+      <c r="B29" s="60"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="30"/>
+      <c r="F29" s="46">
         <v>10000</v>
       </c>
-      <c r="G29" s="34"/>
-      <c r="H29" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="I29" s="34"/>
-      <c r="J29" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="K29" s="34"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="30"/>
+      <c r="J29" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="K29" s="30"/>
       <c r="L29" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q29" s="66"/>
+        <v>12</v>
+      </c>
+      <c r="Q29" s="62"/>
     </row>
     <row r="30" spans="1:17" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
-      <c r="B30" s="64"/>
-      <c r="C30" s="80"/>
-      <c r="D30" s="52"/>
+      <c r="B30" s="60"/>
+      <c r="C30" s="73"/>
+      <c r="D30" s="37"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
@@ -6234,52 +6444,52 @@
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
-      <c r="L30" s="53"/>
+      <c r="L30" s="38"/>
       <c r="Q30" s="23"/>
     </row>
     <row r="31" spans="1:17" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
-      <c r="B31" s="64"/>
-      <c r="C31" s="71"/>
+      <c r="B31" s="60"/>
+      <c r="C31" s="67"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
       <c r="L31" s="10"/>
     </row>
     <row r="32" spans="1:17" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
-      <c r="B32" s="64"/>
-      <c r="C32" s="71"/>
-      <c r="D32" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="34"/>
-      <c r="F32" s="48">
+      <c r="B32" s="60"/>
+      <c r="C32" s="67"/>
+      <c r="D32" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="30"/>
+      <c r="F32" s="44">
         <v>10000</v>
       </c>
-      <c r="G32" s="34"/>
-      <c r="H32" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="I32" s="34"/>
-      <c r="J32" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="K32" s="34"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="30"/>
+      <c r="J32" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="K32" s="30"/>
       <c r="L32" s="12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
-      <c r="B33" s="64"/>
-      <c r="C33" s="80"/>
-      <c r="D33" s="52"/>
+      <c r="B33" s="60"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="37"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
@@ -6287,51 +6497,51 @@
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
-      <c r="L33" s="53"/>
+      <c r="L33" s="38"/>
     </row>
     <row r="34" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
-      <c r="B34" s="64"/>
-      <c r="C34" s="71"/>
+      <c r="B34" s="60"/>
+      <c r="C34" s="67"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
       <c r="L34" s="10"/>
     </row>
     <row r="35" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
-      <c r="B35" s="64"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" s="34"/>
-      <c r="F35" s="44">
+      <c r="B35" s="60"/>
+      <c r="C35" s="67"/>
+      <c r="D35" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="30"/>
+      <c r="F35" s="47">
         <v>10000</v>
       </c>
-      <c r="G35" s="34"/>
-      <c r="H35" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="I35" s="34"/>
-      <c r="J35" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="K35" s="34"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="30"/>
+      <c r="J35" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="K35" s="30"/>
       <c r="L35" s="12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
-      <c r="B36" s="64"/>
-      <c r="C36" s="80"/>
-      <c r="D36" s="52"/>
+      <c r="B36" s="60"/>
+      <c r="C36" s="73"/>
+      <c r="D36" s="37"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
@@ -6339,81 +6549,81 @@
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
-      <c r="L36" s="53"/>
+      <c r="L36" s="38"/>
     </row>
     <row r="37" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
-      <c r="B37" s="64"/>
-      <c r="C37" s="71"/>
+      <c r="B37" s="60"/>
+      <c r="C37" s="67"/>
       <c r="D37" s="2"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
       <c r="H37" s="9"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="34"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
       <c r="L37" s="10"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
-      <c r="B38" s="64"/>
-      <c r="C38" s="71"/>
-      <c r="D38" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
+      <c r="B38" s="60"/>
+      <c r="C38" s="67"/>
+      <c r="D38" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
       <c r="H38" s="9"/>
-      <c r="I38" s="34"/>
-      <c r="J38" s="34"/>
-      <c r="K38" s="34"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
       <c r="L38" s="10"/>
     </row>
     <row r="39" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
-      <c r="B39" s="64"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="34"/>
+      <c r="B39" s="60"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
       <c r="H39" s="9"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="34"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
       <c r="L39" s="10"/>
     </row>
     <row r="40" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
-      <c r="B40" s="64"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" s="34"/>
-      <c r="F40" s="49">
+      <c r="B40" s="60"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="30"/>
+      <c r="F40" s="48">
         <v>10000</v>
       </c>
-      <c r="G40" s="34"/>
-      <c r="H40" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="I40" s="34"/>
-      <c r="J40" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="K40" s="34"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="I40" s="30"/>
+      <c r="J40" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="K40" s="30"/>
       <c r="L40" s="12" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
-      <c r="B41" s="64"/>
-      <c r="C41" s="50"/>
-      <c r="D41" s="31"/>
+      <c r="B41" s="60"/>
+      <c r="C41" s="35"/>
+      <c r="D41" s="27"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
@@ -6421,51 +6631,51 @@
       <c r="I41" s="7"/>
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
-      <c r="L41" s="53"/>
+      <c r="L41" s="38"/>
     </row>
     <row r="42" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
-      <c r="B42" s="64"/>
-      <c r="C42" s="50"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="34"/>
+      <c r="B42" s="60"/>
+      <c r="C42" s="35"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
       <c r="H42" s="9"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
       <c r="L42" s="10"/>
     </row>
     <row r="43" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
-      <c r="B43" s="64"/>
-      <c r="C43" s="50"/>
-      <c r="D43" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="E43" s="34"/>
-      <c r="F43" s="54">
+      <c r="B43" s="60"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" s="30"/>
+      <c r="F43" s="50">
         <v>1</v>
       </c>
-      <c r="G43" s="34"/>
-      <c r="H43" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="I43" s="34"/>
-      <c r="J43" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="K43" s="34"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I43" s="30"/>
+      <c r="J43" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="K43" s="30"/>
       <c r="L43" s="12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
-      <c r="B44" s="64"/>
-      <c r="C44" s="50"/>
-      <c r="D44" s="31"/>
+      <c r="B44" s="60"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="27"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
@@ -6473,12 +6683,12 @@
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
-      <c r="L44" s="53"/>
+      <c r="L44" s="38"/>
     </row>
     <row r="45" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
-      <c r="B45" s="64"/>
-      <c r="C45" s="50"/>
+      <c r="B45" s="60"/>
+      <c r="C45" s="35"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
@@ -6491,8 +6701,8 @@
     </row>
     <row r="46" spans="1:12" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
-      <c r="B46" s="65"/>
-      <c r="C46" s="51"/>
+      <c r="B46" s="61"/>
+      <c r="C46" s="36"/>
       <c r="D46" s="13"/>
       <c r="E46" s="13"/>
       <c r="F46" s="13"/>
@@ -6505,8 +6715,8 @@
     </row>
     <row r="47" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
-      <c r="B47" s="63" t="s">
-        <v>4</v>
+      <c r="B47" s="59" t="s">
+        <v>6</v>
       </c>
       <c r="C47" s="15"/>
       <c r="D47" s="15"/>
@@ -6521,69 +6731,69 @@
     </row>
     <row r="48" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
-      <c r="B48" s="64"/>
+      <c r="B48" s="60"/>
       <c r="C48" s="5"/>
       <c r="D48" s="6"/>
-      <c r="E48" s="67" t="s">
-        <v>5</v>
-      </c>
-      <c r="F48" s="68"/>
-      <c r="G48" s="69"/>
+      <c r="E48" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="64"/>
+      <c r="G48" s="65"/>
       <c r="H48" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I48" s="67" t="s">
-        <v>7</v>
-      </c>
-      <c r="J48" s="68"/>
-      <c r="K48" s="69"/>
+        <v>9</v>
+      </c>
+      <c r="I48" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="J48" s="64"/>
+      <c r="K48" s="65"/>
       <c r="L48" s="11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
-      <c r="B49" s="64"/>
-      <c r="C49" s="70"/>
+      <c r="B49" s="60"/>
+      <c r="C49" s="66"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="34"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="34"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
       <c r="H49" s="8"/>
-      <c r="I49" s="34"/>
-      <c r="J49" s="34"/>
-      <c r="K49" s="34"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
       <c r="L49" s="10"/>
     </row>
     <row r="50" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
-      <c r="B50" s="64"/>
-      <c r="C50" s="71"/>
-      <c r="D50" s="35" t="s">
+      <c r="B50" s="60"/>
+      <c r="C50" s="67"/>
+      <c r="D50" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" s="30"/>
+      <c r="F50" s="44">
+        <v>10000</v>
+      </c>
+      <c r="G50" s="30"/>
+      <c r="H50" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="E50" s="34"/>
-      <c r="F50" s="48">
-        <v>10000</v>
-      </c>
-      <c r="G50" s="34"/>
-      <c r="H50" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="I50" s="34"/>
-      <c r="J50" s="55" t="s">
-        <v>10</v>
-      </c>
-      <c r="K50" s="34"/>
+      <c r="I50" s="30"/>
+      <c r="J50" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="K50" s="30"/>
       <c r="L50" s="12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
-      <c r="B51" s="64"/>
-      <c r="C51" s="80"/>
-      <c r="D51" s="52"/>
+      <c r="B51" s="60"/>
+      <c r="C51" s="73"/>
+      <c r="D51" s="37"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
@@ -6591,51 +6801,51 @@
       <c r="I51" s="7"/>
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
-      <c r="L51" s="53"/>
+      <c r="L51" s="38"/>
     </row>
     <row r="52" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
-      <c r="B52" s="64"/>
-      <c r="C52" s="71"/>
+      <c r="B52" s="60"/>
+      <c r="C52" s="67"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="34"/>
-      <c r="F52" s="34"/>
-      <c r="G52" s="34"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
       <c r="H52" s="9"/>
-      <c r="I52" s="34"/>
-      <c r="J52" s="34"/>
-      <c r="K52" s="34"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
       <c r="L52" s="10"/>
     </row>
     <row r="53" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
-      <c r="B53" s="64"/>
-      <c r="C53" s="71"/>
-      <c r="D53" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="E53" s="34"/>
-      <c r="F53" s="48">
+      <c r="B53" s="60"/>
+      <c r="C53" s="67"/>
+      <c r="D53" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" s="30"/>
+      <c r="F53" s="44">
         <v>10000</v>
       </c>
-      <c r="G53" s="34"/>
-      <c r="H53" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="I53" s="34"/>
-      <c r="J53" s="55" t="s">
-        <v>10</v>
-      </c>
-      <c r="K53" s="34"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" s="30"/>
+      <c r="J53" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="K53" s="30"/>
       <c r="L53" s="12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
-      <c r="B54" s="64"/>
-      <c r="C54" s="80"/>
-      <c r="D54" s="52"/>
+      <c r="B54" s="60"/>
+      <c r="C54" s="73"/>
+      <c r="D54" s="37"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
@@ -6643,51 +6853,51 @@
       <c r="I54" s="7"/>
       <c r="J54" s="7"/>
       <c r="K54" s="7"/>
-      <c r="L54" s="53"/>
+      <c r="L54" s="38"/>
     </row>
     <row r="55" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
-      <c r="B55" s="64"/>
-      <c r="C55" s="71"/>
+      <c r="B55" s="60"/>
+      <c r="C55" s="67"/>
       <c r="D55" s="2"/>
-      <c r="E55" s="34"/>
-      <c r="F55" s="34"/>
-      <c r="G55" s="34"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
       <c r="H55" s="9"/>
-      <c r="I55" s="34"/>
-      <c r="J55" s="34"/>
-      <c r="K55" s="34"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
       <c r="L55" s="10"/>
     </row>
     <row r="56" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
-      <c r="B56" s="64"/>
-      <c r="C56" s="71"/>
-      <c r="D56" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="E56" s="34"/>
-      <c r="F56" s="48">
+      <c r="B56" s="60"/>
+      <c r="C56" s="67"/>
+      <c r="D56" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E56" s="30"/>
+      <c r="F56" s="44">
         <v>10000</v>
       </c>
-      <c r="G56" s="34"/>
-      <c r="H56" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="I56" s="34"/>
-      <c r="J56" s="55" t="s">
-        <v>10</v>
-      </c>
-      <c r="K56" s="34"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" s="30"/>
+      <c r="J56" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="K56" s="30"/>
       <c r="L56" s="12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
-      <c r="B57" s="64"/>
-      <c r="C57" s="80"/>
-      <c r="D57" s="52"/>
+      <c r="B57" s="60"/>
+      <c r="C57" s="73"/>
+      <c r="D57" s="37"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
       <c r="G57" s="7"/>
@@ -6695,51 +6905,51 @@
       <c r="I57" s="7"/>
       <c r="J57" s="7"/>
       <c r="K57" s="7"/>
-      <c r="L57" s="53"/>
+      <c r="L57" s="38"/>
     </row>
     <row r="58" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
-      <c r="B58" s="64"/>
-      <c r="C58" s="71"/>
+      <c r="B58" s="60"/>
+      <c r="C58" s="67"/>
       <c r="D58" s="2"/>
-      <c r="E58" s="34"/>
-      <c r="F58" s="34"/>
-      <c r="G58" s="34"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
       <c r="H58" s="9"/>
-      <c r="I58" s="34"/>
-      <c r="J58" s="34"/>
-      <c r="K58" s="34"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
       <c r="L58" s="10"/>
     </row>
     <row r="59" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
-      <c r="B59" s="64"/>
-      <c r="C59" s="71"/>
-      <c r="D59" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="E59" s="34"/>
-      <c r="F59" s="48">
+      <c r="B59" s="60"/>
+      <c r="C59" s="67"/>
+      <c r="D59" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="30"/>
+      <c r="F59" s="44">
         <v>10000</v>
       </c>
-      <c r="G59" s="34"/>
-      <c r="H59" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="I59" s="34"/>
-      <c r="J59" s="55" t="s">
-        <v>10</v>
-      </c>
-      <c r="K59" s="34"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" s="30"/>
+      <c r="J59" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="K59" s="30"/>
       <c r="L59" s="12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
-      <c r="B60" s="64"/>
-      <c r="C60" s="80"/>
-      <c r="D60" s="52"/>
+      <c r="B60" s="60"/>
+      <c r="C60" s="73"/>
+      <c r="D60" s="37"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
@@ -6747,81 +6957,81 @@
       <c r="I60" s="7"/>
       <c r="J60" s="7"/>
       <c r="K60" s="7"/>
-      <c r="L60" s="53"/>
+      <c r="L60" s="38"/>
     </row>
     <row r="61" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
-      <c r="B61" s="64"/>
-      <c r="C61" s="71"/>
+      <c r="B61" s="60"/>
+      <c r="C61" s="67"/>
       <c r="D61" s="2"/>
-      <c r="E61" s="34"/>
-      <c r="F61" s="34"/>
-      <c r="G61" s="34"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
       <c r="H61" s="9"/>
-      <c r="I61" s="34"/>
-      <c r="J61" s="34"/>
-      <c r="K61" s="34"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
       <c r="L61" s="10"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
-      <c r="B62" s="64"/>
-      <c r="C62" s="71"/>
-      <c r="D62" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="E62" s="34"/>
-      <c r="F62" s="34"/>
-      <c r="G62" s="34"/>
+      <c r="B62" s="60"/>
+      <c r="C62" s="67"/>
+      <c r="D62" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="30"/>
       <c r="H62" s="9"/>
-      <c r="I62" s="34"/>
-      <c r="J62" s="34"/>
-      <c r="K62" s="34"/>
+      <c r="I62" s="30"/>
+      <c r="J62" s="30"/>
+      <c r="K62" s="30"/>
       <c r="L62" s="10"/>
     </row>
     <row r="63" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
-      <c r="B63" s="64"/>
-      <c r="C63" s="50"/>
-      <c r="D63" s="35"/>
-      <c r="E63" s="34"/>
-      <c r="F63" s="34"/>
-      <c r="G63" s="34"/>
+      <c r="B63" s="60"/>
+      <c r="C63" s="35"/>
+      <c r="D63" s="31"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="30"/>
       <c r="H63" s="9"/>
-      <c r="I63" s="34"/>
-      <c r="J63" s="34"/>
-      <c r="K63" s="34"/>
+      <c r="I63" s="30"/>
+      <c r="J63" s="30"/>
+      <c r="K63" s="30"/>
       <c r="L63" s="10"/>
     </row>
     <row r="64" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
-      <c r="B64" s="64"/>
-      <c r="C64" s="50"/>
-      <c r="D64" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="E64" s="34"/>
-      <c r="F64" s="49">
+      <c r="B64" s="60"/>
+      <c r="C64" s="35"/>
+      <c r="D64" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E64" s="30"/>
+      <c r="F64" s="48">
         <v>10000</v>
       </c>
-      <c r="G64" s="34"/>
-      <c r="H64" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="I64" s="34"/>
-      <c r="J64" s="55" t="s">
-        <v>10</v>
-      </c>
-      <c r="K64" s="34"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="I64" s="30"/>
+      <c r="J64" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="K64" s="30"/>
       <c r="L64" s="12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
-      <c r="B65" s="64"/>
-      <c r="C65" s="50"/>
-      <c r="D65" s="31"/>
+      <c r="B65" s="60"/>
+      <c r="C65" s="35"/>
+      <c r="D65" s="27"/>
       <c r="E65" s="7"/>
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
@@ -6829,51 +7039,51 @@
       <c r="I65" s="7"/>
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
-      <c r="L65" s="53"/>
+      <c r="L65" s="38"/>
     </row>
     <row r="66" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
-      <c r="B66" s="64"/>
-      <c r="C66" s="50"/>
-      <c r="D66" s="35"/>
-      <c r="E66" s="34"/>
-      <c r="F66" s="34"/>
-      <c r="G66" s="34"/>
+      <c r="B66" s="60"/>
+      <c r="C66" s="35"/>
+      <c r="D66" s="31"/>
+      <c r="E66" s="30"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="30"/>
       <c r="H66" s="9"/>
-      <c r="I66" s="34"/>
-      <c r="J66" s="34"/>
-      <c r="K66" s="34"/>
+      <c r="I66" s="30"/>
+      <c r="J66" s="30"/>
+      <c r="K66" s="30"/>
       <c r="L66" s="10"/>
     </row>
     <row r="67" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
-      <c r="B67" s="64"/>
-      <c r="C67" s="50"/>
-      <c r="D67" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="E67" s="34"/>
-      <c r="F67" s="48">
+      <c r="B67" s="60"/>
+      <c r="C67" s="35"/>
+      <c r="D67" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E67" s="30"/>
+      <c r="F67" s="44">
         <v>10000</v>
       </c>
-      <c r="G67" s="34"/>
-      <c r="H67" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="I67" s="34"/>
-      <c r="J67" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="K67" s="34"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="I67" s="30"/>
+      <c r="J67" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="K67" s="30"/>
       <c r="L67" s="12" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
-      <c r="B68" s="64"/>
-      <c r="C68" s="50"/>
-      <c r="D68" s="31"/>
+      <c r="B68" s="60"/>
+      <c r="C68" s="35"/>
+      <c r="D68" s="27"/>
       <c r="E68" s="7"/>
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
@@ -6881,12 +7091,12 @@
       <c r="I68" s="7"/>
       <c r="J68" s="7"/>
       <c r="K68" s="7"/>
-      <c r="L68" s="53"/>
+      <c r="L68" s="38"/>
     </row>
     <row r="69" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
-      <c r="B69" s="64"/>
-      <c r="C69" s="50"/>
+      <c r="B69" s="60"/>
+      <c r="C69" s="35"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
@@ -6899,8 +7109,8 @@
     </row>
     <row r="70" spans="1:12" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
-      <c r="B70" s="65"/>
-      <c r="C70" s="51"/>
+      <c r="B70" s="61"/>
+      <c r="C70" s="36"/>
       <c r="D70" s="13"/>
       <c r="E70" s="13"/>
       <c r="F70" s="13"/>
@@ -6939,40 +7149,40 @@
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
     </row>
-    <row r="73" spans="1:12" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="28.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
-      <c r="B73" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="C73" s="75"/>
-      <c r="D73" s="75"/>
-      <c r="E73" s="75"/>
-      <c r="F73" s="75"/>
-      <c r="G73" s="75"/>
-      <c r="H73" s="75"/>
-      <c r="I73" s="75"/>
-      <c r="J73" s="75"/>
-      <c r="K73" s="75"/>
-      <c r="L73" s="76"/>
+      <c r="B73" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="C73" s="54"/>
+      <c r="D73" s="54"/>
+      <c r="E73" s="54"/>
+      <c r="F73" s="54"/>
+      <c r="G73" s="54"/>
+      <c r="H73" s="54"/>
+      <c r="I73" s="54"/>
+      <c r="J73" s="54"/>
+      <c r="K73" s="54"/>
+      <c r="L73" s="55"/>
     </row>
     <row r="74" spans="1:12" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
-      <c r="B74" s="77"/>
-      <c r="C74" s="78"/>
-      <c r="D74" s="78"/>
-      <c r="E74" s="78"/>
-      <c r="F74" s="78"/>
-      <c r="G74" s="78"/>
-      <c r="H74" s="78"/>
-      <c r="I74" s="78"/>
-      <c r="J74" s="78"/>
-      <c r="K74" s="78"/>
-      <c r="L74" s="79"/>
+      <c r="B74" s="70"/>
+      <c r="C74" s="71"/>
+      <c r="D74" s="71"/>
+      <c r="E74" s="71"/>
+      <c r="F74" s="71"/>
+      <c r="G74" s="71"/>
+      <c r="H74" s="71"/>
+      <c r="I74" s="71"/>
+      <c r="J74" s="71"/>
+      <c r="K74" s="71"/>
+      <c r="L74" s="72"/>
     </row>
     <row r="75" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
-      <c r="B75" s="73" t="s">
-        <v>12</v>
+      <c r="B75" s="69" t="s">
+        <v>15</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
@@ -6987,69 +7197,69 @@
     </row>
     <row r="76" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
-      <c r="B76" s="64"/>
+      <c r="B76" s="60"/>
       <c r="C76" s="5"/>
       <c r="D76" s="6"/>
-      <c r="E76" s="67" t="s">
-        <v>5</v>
-      </c>
-      <c r="F76" s="68"/>
-      <c r="G76" s="69"/>
+      <c r="E76" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" s="64"/>
+      <c r="G76" s="65"/>
       <c r="H76" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I76" s="67" t="s">
-        <v>7</v>
-      </c>
-      <c r="J76" s="68"/>
-      <c r="K76" s="69"/>
+        <v>9</v>
+      </c>
+      <c r="I76" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="J76" s="64"/>
+      <c r="K76" s="65"/>
       <c r="L76" s="11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
-      <c r="B77" s="64"/>
-      <c r="C77" s="70"/>
+      <c r="B77" s="60"/>
+      <c r="C77" s="66"/>
       <c r="D77" s="2"/>
-      <c r="E77" s="34"/>
-      <c r="F77" s="34"/>
-      <c r="G77" s="34"/>
+      <c r="E77" s="30"/>
+      <c r="F77" s="30"/>
+      <c r="G77" s="30"/>
       <c r="H77" s="8"/>
-      <c r="I77" s="34"/>
-      <c r="J77" s="34"/>
-      <c r="K77" s="34"/>
+      <c r="I77" s="30"/>
+      <c r="J77" s="30"/>
+      <c r="K77" s="30"/>
       <c r="L77" s="10"/>
     </row>
     <row r="78" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
-      <c r="B78" s="64"/>
-      <c r="C78" s="71"/>
-      <c r="D78" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="E78" s="34"/>
-      <c r="F78" s="48">
+      <c r="B78" s="60"/>
+      <c r="C78" s="67"/>
+      <c r="D78" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="E78" s="30"/>
+      <c r="F78" s="44">
         <v>10000</v>
       </c>
-      <c r="G78" s="34"/>
-      <c r="H78" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="I78" s="34"/>
-      <c r="J78" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="K78" s="34"/>
+      <c r="G78" s="30"/>
+      <c r="H78" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I78" s="30"/>
+      <c r="J78" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="K78" s="30"/>
       <c r="L78" s="12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
-      <c r="B79" s="64"/>
-      <c r="C79" s="80"/>
-      <c r="D79" s="52"/>
+      <c r="B79" s="60"/>
+      <c r="C79" s="73"/>
+      <c r="D79" s="37"/>
       <c r="E79" s="7"/>
       <c r="F79" s="7"/>
       <c r="G79" s="7"/>
@@ -7057,51 +7267,51 @@
       <c r="I79" s="7"/>
       <c r="J79" s="7"/>
       <c r="K79" s="7"/>
-      <c r="L79" s="53"/>
+      <c r="L79" s="38"/>
     </row>
     <row r="80" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
-      <c r="B80" s="64"/>
-      <c r="C80" s="71"/>
+      <c r="B80" s="60"/>
+      <c r="C80" s="67"/>
       <c r="D80" s="2"/>
-      <c r="E80" s="34"/>
-      <c r="F80" s="34"/>
-      <c r="G80" s="34"/>
+      <c r="E80" s="30"/>
+      <c r="F80" s="30"/>
+      <c r="G80" s="30"/>
       <c r="H80" s="9"/>
-      <c r="I80" s="34"/>
-      <c r="J80" s="34"/>
-      <c r="K80" s="34"/>
+      <c r="I80" s="30"/>
+      <c r="J80" s="30"/>
+      <c r="K80" s="30"/>
       <c r="L80" s="10"/>
     </row>
     <row r="81" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
-      <c r="B81" s="64"/>
-      <c r="C81" s="71"/>
-      <c r="D81" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="E81" s="34"/>
-      <c r="F81" s="48">
+      <c r="B81" s="60"/>
+      <c r="C81" s="67"/>
+      <c r="D81" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="E81" s="30"/>
+      <c r="F81" s="44">
         <v>10000</v>
       </c>
-      <c r="G81" s="34"/>
-      <c r="H81" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="I81" s="34"/>
-      <c r="J81" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="K81" s="34"/>
+      <c r="G81" s="30"/>
+      <c r="H81" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I81" s="30"/>
+      <c r="J81" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="K81" s="30"/>
       <c r="L81" s="12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
-      <c r="B82" s="81"/>
-      <c r="C82" s="80"/>
-      <c r="D82" s="52"/>
+      <c r="B82" s="74"/>
+      <c r="C82" s="73"/>
+      <c r="D82" s="37"/>
       <c r="E82" s="7"/>
       <c r="F82" s="7"/>
       <c r="G82" s="7"/>
@@ -7109,12 +7319,12 @@
       <c r="I82" s="7"/>
       <c r="J82" s="7"/>
       <c r="K82" s="7"/>
-      <c r="L82" s="53"/>
+      <c r="L82" s="38"/>
     </row>
     <row r="83" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
-      <c r="B83" s="73" t="s">
-        <v>4</v>
+      <c r="B83" s="69" t="s">
+        <v>6</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
@@ -7129,69 +7339,69 @@
     </row>
     <row r="84" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
-      <c r="B84" s="64"/>
+      <c r="B84" s="60"/>
       <c r="C84" s="5"/>
       <c r="D84" s="6"/>
-      <c r="E84" s="67" t="s">
-        <v>5</v>
-      </c>
-      <c r="F84" s="68"/>
-      <c r="G84" s="69"/>
+      <c r="E84" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="F84" s="64"/>
+      <c r="G84" s="65"/>
       <c r="H84" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I84" s="67" t="s">
-        <v>7</v>
-      </c>
-      <c r="J84" s="68"/>
-      <c r="K84" s="69"/>
+        <v>9</v>
+      </c>
+      <c r="I84" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="J84" s="64"/>
+      <c r="K84" s="65"/>
       <c r="L84" s="11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
-      <c r="B85" s="64"/>
-      <c r="C85" s="70"/>
+      <c r="B85" s="60"/>
+      <c r="C85" s="66"/>
       <c r="D85" s="2"/>
-      <c r="E85" s="34"/>
-      <c r="F85" s="34"/>
-      <c r="G85" s="34"/>
+      <c r="E85" s="30"/>
+      <c r="F85" s="30"/>
+      <c r="G85" s="30"/>
       <c r="H85" s="8"/>
-      <c r="I85" s="34"/>
-      <c r="J85" s="34"/>
-      <c r="K85" s="34"/>
+      <c r="I85" s="30"/>
+      <c r="J85" s="30"/>
+      <c r="K85" s="30"/>
       <c r="L85" s="10"/>
     </row>
     <row r="86" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
-      <c r="B86" s="64"/>
-      <c r="C86" s="71"/>
-      <c r="D86" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="E86" s="34"/>
-      <c r="F86" s="48">
+      <c r="B86" s="60"/>
+      <c r="C86" s="67"/>
+      <c r="D86" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="E86" s="30"/>
+      <c r="F86" s="44">
         <v>10000</v>
       </c>
-      <c r="G86" s="34"/>
-      <c r="H86" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="I86" s="34"/>
-      <c r="J86" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="K86" s="34"/>
+      <c r="G86" s="30"/>
+      <c r="H86" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I86" s="30"/>
+      <c r="J86" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="K86" s="30"/>
       <c r="L86" s="12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
-      <c r="B87" s="64"/>
-      <c r="C87" s="80"/>
-      <c r="D87" s="52"/>
+      <c r="B87" s="60"/>
+      <c r="C87" s="73"/>
+      <c r="D87" s="37"/>
       <c r="E87" s="7"/>
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
@@ -7199,50 +7409,50 @@
       <c r="I87" s="7"/>
       <c r="J87" s="7"/>
       <c r="K87" s="7"/>
-      <c r="L87" s="53"/>
+      <c r="L87" s="38"/>
     </row>
     <row r="88" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
-      <c r="B88" s="64"/>
-      <c r="C88" s="71"/>
+      <c r="B88" s="60"/>
+      <c r="C88" s="67"/>
       <c r="D88" s="2"/>
-      <c r="E88" s="34"/>
-      <c r="F88" s="34"/>
-      <c r="G88" s="34"/>
+      <c r="E88" s="30"/>
+      <c r="F88" s="30"/>
+      <c r="G88" s="30"/>
       <c r="H88" s="9"/>
-      <c r="I88" s="34"/>
-      <c r="J88" s="34"/>
-      <c r="K88" s="34"/>
+      <c r="I88" s="30"/>
+      <c r="J88" s="30"/>
+      <c r="K88" s="30"/>
       <c r="L88" s="10"/>
     </row>
     <row r="89" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
-      <c r="B89" s="64"/>
-      <c r="C89" s="71"/>
-      <c r="D89" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="E89" s="34"/>
-      <c r="F89" s="48">
+      <c r="B89" s="60"/>
+      <c r="C89" s="67"/>
+      <c r="D89" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="E89" s="30"/>
+      <c r="F89" s="44">
         <v>10000</v>
       </c>
-      <c r="G89" s="34"/>
-      <c r="H89" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="I89" s="34"/>
-      <c r="J89" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="K89" s="34"/>
+      <c r="G89" s="30"/>
+      <c r="H89" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I89" s="30"/>
+      <c r="J89" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="K89" s="30"/>
       <c r="L89" s="12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
-      <c r="B90" s="65"/>
-      <c r="C90" s="72"/>
+      <c r="B90" s="61"/>
+      <c r="C90" s="68"/>
       <c r="D90" s="13"/>
       <c r="E90" s="18"/>
       <c r="F90" s="18"/>
@@ -8038,7 +8248,8 @@
       <c r="L146" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/Chmw4zSd3RJ1wMxaE3DbLzaXzujPt7FFSOhA/pH0mLBB1mHkoDZPXarzxdqU85i1j82PBx4Eb6X22eWPx1tJQ==" saltValue="Wv6Y+aUwtP+n2PtDScGYIg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="jUzRW1wZU4UKDlrc+ZcjfI1CGFMPpb3WBOiNrGujdLz4z6mGk5OrV9Q3LSR9/vcnYNn7Umyfq3hCTh4LwP0m/Q==" saltValue="0LYgXzE3BB0FL5cMFmUsdQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0"/>
+  <dataConsolidate/>
   <mergeCells count="43">
     <mergeCell ref="B83:B90"/>
     <mergeCell ref="E84:G84"/>
@@ -8085,13 +8296,17 @@
     <mergeCell ref="C16:C18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <customProperties>
+    <customPr name="IbpWorksheetKeyString_GUID" r:id="rId2"/>
+  </customProperties>
+  <drawing r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24599" r:id="rId3" name="cbApplyOddEvenFormatting">
-          <controlPr defaultSize="0" autoFill="0" autoLine="0" r:id="rId4">
+        <control shapeId="27671" r:id="rId5" name="cbApplyOddEvenFormatting">
+          <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId6">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
@@ -8110,13 +8325,13 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="24599" r:id="rId3" name="cbApplyOddEvenFormatting"/>
+        <control shapeId="27671" r:id="rId5" name="cbApplyOddEvenFormatting"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24583" r:id="rId5" name="cbApplyMemberFormatting">
-          <controlPr defaultSize="0" autoFill="0" autoLine="0" r:id="rId6">
+        <control shapeId="27655" r:id="rId7" name="cbApplyMemberFormatting">
+          <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId8">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
@@ -8135,13 +8350,13 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="24583" r:id="rId5" name="cbApplyMemberFormatting"/>
+        <control shapeId="27655" r:id="rId7" name="cbApplyMemberFormatting"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24577" r:id="rId7" name="cbApplyLevelFormatting">
-          <controlPr defaultSize="0" autoFill="0" autoLine="0" r:id="rId6">
+        <control shapeId="27649" r:id="rId9" name="cbApplyLevelFormatting">
+          <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId10">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
@@ -8160,12 +8375,12 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="24577" r:id="rId7" name="cbApplyLevelFormatting"/>
+        <control shapeId="27649" r:id="rId9" name="cbApplyLevelFormatting"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24578" r:id="rId8" name="Group Box 2">
+        <control shapeId="27650" r:id="rId11" name="Group Box 2">
           <controlPr defaultSize="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8176,7 +8391,7 @@
               </from>
               <to>
                 <xdr:col>3</xdr:col>
-                <xdr:colOff>2724150</xdr:colOff>
+                <xdr:colOff>2733675</xdr:colOff>
                 <xdr:row>6</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </to>
@@ -8187,7 +8402,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24579" r:id="rId9" name="obLevelRowFirst">
+        <control shapeId="27651" r:id="rId12" name="obLevelRowFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1">
               <from>
@@ -8209,7 +8424,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24580" r:id="rId10" name="obLevelColumnFirst">
+        <control shapeId="27652" r:id="rId13" name="obLevelColumnFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1">
               <from>
@@ -8220,7 +8435,7 @@
               </from>
               <to>
                 <xdr:col>3</xdr:col>
-                <xdr:colOff>371475</xdr:colOff>
+                <xdr:colOff>390525</xdr:colOff>
                 <xdr:row>5</xdr:row>
                 <xdr:rowOff>295275</xdr:rowOff>
               </to>
@@ -8231,7 +8446,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24581" r:id="rId11" name="cbUseDefaultLevelFirst">
+        <control shapeId="27653" r:id="rId14" name="cbUseDefaultLevelFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8241,8 +8456,8 @@
                 <xdr:rowOff>9525</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1057275</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
                 <xdr:row>17</xdr:row>
                 <xdr:rowOff>47625</xdr:rowOff>
               </to>
@@ -8253,7 +8468,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24582" r:id="rId12" name="cbUseDefaultLevelSecond">
+        <control shapeId="27654" r:id="rId15" name="cbUseDefaultLevelSecond">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8263,8 +8478,8 @@
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1057275</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
                 <xdr:row>11</xdr:row>
                 <xdr:rowOff>38100</xdr:rowOff>
               </to>
@@ -8275,7 +8490,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24584" r:id="rId13" name="Group Box 8">
+        <control shapeId="27656" r:id="rId16" name="Group Box 8">
           <controlPr defaultSize="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8286,9 +8501,9 @@
               </from>
               <to>
                 <xdr:col>12</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
+                <xdr:colOff>28575</xdr:colOff>
                 <xdr:row>22</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </controlPr>
@@ -8297,7 +8512,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24585" r:id="rId14" name="obMemberRowFirst">
+        <control shapeId="27657" r:id="rId17" name="obMemberRowFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1">
               <from>
@@ -8319,7 +8534,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24586" r:id="rId15" name="obMemberColumnFirst">
+        <control shapeId="27658" r:id="rId18" name="obMemberColumnFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1">
               <from>
@@ -8330,7 +8545,7 @@
               </from>
               <to>
                 <xdr:col>3</xdr:col>
-                <xdr:colOff>371475</xdr:colOff>
+                <xdr:colOff>390525</xdr:colOff>
                 <xdr:row>21</xdr:row>
                 <xdr:rowOff>295275</xdr:rowOff>
               </to>
@@ -8341,7 +8556,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24587" r:id="rId16" name="cbApplyCalculatedMemberFirst">
+        <control shapeId="27659" r:id="rId19" name="cbApplyCalculatedMemberFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8351,8 +8566,8 @@
                 <xdr:rowOff>209550</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1057275</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
                 <xdr:row>26</xdr:row>
                 <xdr:rowOff>38100</xdr:rowOff>
               </to>
@@ -8363,7 +8578,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24588" r:id="rId17" name="cbApplyImputableMemberFirst">
+        <control shapeId="27660" r:id="rId20" name="cbApplyImputableMemberFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8373,8 +8588,8 @@
                 <xdr:rowOff>57150</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1057275</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
                 <xdr:row>29</xdr:row>
                 <xdr:rowOff>38100</xdr:rowOff>
               </to>
@@ -8385,7 +8600,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24589" r:id="rId18" name="cbApplyLocalMemberFirst">
+        <control shapeId="27661" r:id="rId21" name="cbApplyLocalMemberFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8395,8 +8610,8 @@
                 <xdr:rowOff>57150</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1057275</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
                 <xdr:row>32</xdr:row>
                 <xdr:rowOff>38100</xdr:rowOff>
               </to>
@@ -8407,7 +8622,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24590" r:id="rId19" name="cbApplyChangedMemberFirst">
+        <control shapeId="27662" r:id="rId22" name="cbApplyChangedMemberFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8417,8 +8632,8 @@
                 <xdr:rowOff>57150</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1057275</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
                 <xdr:row>35</xdr:row>
                 <xdr:rowOff>38100</xdr:rowOff>
               </to>
@@ -8429,7 +8644,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24591" r:id="rId20" name="cbApplySpecificMemberFirst">
+        <control shapeId="27663" r:id="rId23" name="cbApplySpecificMemberFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8439,8 +8654,8 @@
                 <xdr:rowOff>47625</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1057275</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
                 <xdr:row>38</xdr:row>
                 <xdr:rowOff>9525</xdr:rowOff>
               </to>
@@ -8451,7 +8666,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24592" r:id="rId21" name="AddMemberFirst">
+        <control shapeId="27664" r:id="rId24" name="AddMemberFirst">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -8473,7 +8688,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24593" r:id="rId22" name="cbApplyCalculatedMemberSecond">
+        <control shapeId="27665" r:id="rId25" name="cbApplyCalculatedMemberSecond">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8483,8 +8698,8 @@
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1057275</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
                 <xdr:row>50</xdr:row>
                 <xdr:rowOff>38100</xdr:rowOff>
               </to>
@@ -8495,7 +8710,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24594" r:id="rId23" name="cbApplyImputableMemberSecond">
+        <control shapeId="27666" r:id="rId26" name="cbApplyImputableMemberSecond">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8505,8 +8720,8 @@
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1057275</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
                 <xdr:row>53</xdr:row>
                 <xdr:rowOff>38100</xdr:rowOff>
               </to>
@@ -8517,7 +8732,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24595" r:id="rId24" name="cbApplyLocalMemberSecond">
+        <control shapeId="27667" r:id="rId27" name="cbApplyLocalMemberSecond">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8527,8 +8742,8 @@
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1057275</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
                 <xdr:row>56</xdr:row>
                 <xdr:rowOff>38100</xdr:rowOff>
               </to>
@@ -8539,7 +8754,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24596" r:id="rId25" name="cbApplyChangedMemberSecond">
+        <control shapeId="27668" r:id="rId28" name="cbApplyChangedMemberSecond">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8549,8 +8764,8 @@
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1057275</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
                 <xdr:row>59</xdr:row>
                 <xdr:rowOff>38100</xdr:rowOff>
               </to>
@@ -8561,7 +8776,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24597" r:id="rId26" name="cbApplySpecificMemberSecond">
+        <control shapeId="27669" r:id="rId29" name="cbApplySpecificMemberSecond">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8571,8 +8786,8 @@
                 <xdr:rowOff>47625</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1057275</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
                 <xdr:row>62</xdr:row>
                 <xdr:rowOff>38100</xdr:rowOff>
               </to>
@@ -8583,7 +8798,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24598" r:id="rId27" name="AddMemberSecond">
+        <control shapeId="27670" r:id="rId30" name="AddMemberSecond">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -8605,7 +8820,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24600" r:id="rId28" name="Group Box 24">
+        <control shapeId="27672" r:id="rId31" name="Group Box 24">
           <controlPr defaultSize="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8616,7 +8831,7 @@
               </from>
               <to>
                 <xdr:col>12</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
+                <xdr:colOff>28575</xdr:colOff>
                 <xdr:row>74</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </to>
@@ -8627,7 +8842,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24601" r:id="rId29" name="obOddEvenRowFirst">
+        <control shapeId="27673" r:id="rId32" name="obOddEvenRowFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1">
               <from>
@@ -8649,7 +8864,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24602" r:id="rId30" name="obOddEvenColumnFirst">
+        <control shapeId="27674" r:id="rId33" name="obOddEvenColumnFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1">
               <from>
@@ -8660,7 +8875,7 @@
               </from>
               <to>
                 <xdr:col>3</xdr:col>
-                <xdr:colOff>371475</xdr:colOff>
+                <xdr:colOff>390525</xdr:colOff>
                 <xdr:row>73</xdr:row>
                 <xdr:rowOff>276225</xdr:rowOff>
               </to>
@@ -8671,7 +8886,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24603" r:id="rId31" name="cbUseOddFirst">
+        <control shapeId="27675" r:id="rId34" name="cbUseOddFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8681,8 +8896,8 @@
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1057275</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
                 <xdr:row>78</xdr:row>
                 <xdr:rowOff>38100</xdr:rowOff>
               </to>
@@ -8693,7 +8908,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24604" r:id="rId32" name="cbUseEvenFirst">
+        <control shapeId="27676" r:id="rId35" name="cbUseEvenFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8703,8 +8918,8 @@
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1057275</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
                 <xdr:row>81</xdr:row>
                 <xdr:rowOff>38100</xdr:rowOff>
               </to>
@@ -8715,7 +8930,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24605" r:id="rId33" name="cbUseOddSecond">
+        <control shapeId="27677" r:id="rId36" name="cbUseOddSecond">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8725,8 +8940,8 @@
                 <xdr:rowOff>9525</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1057275</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
                 <xdr:row>86</xdr:row>
                 <xdr:rowOff>38100</xdr:rowOff>
               </to>
@@ -8737,7 +8952,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24606" r:id="rId34" name="cbUseEvenSecond">
+        <control shapeId="27678" r:id="rId37" name="cbUseEvenSecond">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8747,8 +8962,8 @@
                 <xdr:rowOff>9525</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>1057275</xdr:colOff>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
                 <xdr:row>89</xdr:row>
                 <xdr:rowOff>38100</xdr:rowOff>
               </to>
@@ -8759,7 +8974,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24607" r:id="rId35" name="AddedMember1_1">
+        <control shapeId="27679" r:id="rId38" name="AddedMember1_1">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -8781,7 +8996,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24608" r:id="rId36" name="ChangeMember1_1">
+        <control shapeId="27680" r:id="rId39" name="ChangeMember1_1">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -8803,7 +9018,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24609" r:id="rId37" name="UpMember1_1">
+        <control shapeId="27681" r:id="rId40" name="UpMember1_1">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -8825,7 +9040,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24610" r:id="rId38" name="DownMember1_1">
+        <control shapeId="27682" r:id="rId41" name="DownMember1_1">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -8847,7 +9062,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24611" r:id="rId39" name="AddedMember1_2">
+        <control shapeId="27683" r:id="rId42" name="AddedMember1_2">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -8869,7 +9084,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24612" r:id="rId40" name="ChangeMember1_2">
+        <control shapeId="27684" r:id="rId43" name="ChangeMember1_2">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -8891,7 +9106,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24613" r:id="rId41" name="UpMember1_2">
+        <control shapeId="27685" r:id="rId44" name="UpMember1_2">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -8913,7 +9128,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24614" r:id="rId42" name="DownMember1_2">
+        <control shapeId="27686" r:id="rId45" name="DownMember1_2">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -8935,7 +9150,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24615" r:id="rId43" name="AddedMember2_1">
+        <control shapeId="27687" r:id="rId46" name="AddedMember2_1">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -8957,7 +9172,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24616" r:id="rId44" name="ChangeMember2_1">
+        <control shapeId="27688" r:id="rId47" name="ChangeMember2_1">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -8979,7 +9194,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24617" r:id="rId45" name="UpMember2_1">
+        <control shapeId="27689" r:id="rId48" name="UpMember2_1">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9001,7 +9216,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24618" r:id="rId46" name="DownMember2_1">
+        <control shapeId="27690" r:id="rId49" name="DownMember2_1">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9023,7 +9238,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24619" r:id="rId47" name="AddedMember2_2">
+        <control shapeId="27691" r:id="rId50" name="AddedMember2_2">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9045,7 +9260,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24620" r:id="rId48" name="ChangeMember2_2">
+        <control shapeId="27692" r:id="rId51" name="ChangeMember2_2">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9067,7 +9282,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24621" r:id="rId49" name="UpMember2_2">
+        <control shapeId="27693" r:id="rId52" name="UpMember2_2">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9089,7 +9304,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="24622" r:id="rId50" name="DownMember2_2">
+        <control shapeId="27694" r:id="rId53" name="DownMember2_2">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9109,6 +9324,72 @@
         </control>
       </mc:Choice>
     </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="27695" r:id="rId54" name="cbApplyLevelFormattingShape">
+          <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>266700</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>57150</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="27696" r:id="rId55" name="cbApplyMemberFormattingShape">
+          <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>266700</xdr:colOff>
+                <xdr:row>20</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>57150</xdr:colOff>
+                <xdr:row>21</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="27697" r:id="rId56" name="cbApplyOddEvenFormattingShape">
+          <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>266700</xdr:colOff>
+                <xdr:row>72</xdr:row>
+                <xdr:rowOff>57150</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>57150</xdr:colOff>
+                <xdr:row>72</xdr:row>
+                <xdr:rowOff>333375</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+    </mc:AlternateContent>
   </controls>
 </worksheet>
 </file>
@@ -9116,311 +9397,125 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:CG6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
     <col min="2" max="9" width="1.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="23" width="13.42578125" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1"/>
+    <col min="12" max="23" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:85" s="26" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="str">
+    <row r="1" spans="1:11" s="40" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="75" t="str">
         <f>" IBP | " &amp;IFERROR(IF(SOP_Favorite_Name&lt;&gt;" ",SOP_Favorite_Name,IF(SOP_Template_Name&lt;&gt;" ",SOP_Template_Name,"Ad Hoc Planning View")),"Offline")</f>
         <v xml:space="preserve"> IBP | Ad Hoc Planning View</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="43"/>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
-      <c r="AB1" s="24"/>
-      <c r="AC1" s="24"/>
-      <c r="AD1" s="24"/>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="25"/>
-      <c r="AH1" s="25"/>
-      <c r="AI1" s="25"/>
-      <c r="AJ1" s="25"/>
-      <c r="AK1" s="25"/>
-      <c r="BR1" s="27"/>
-      <c r="BS1" s="27"/>
-      <c r="BT1" s="27"/>
-      <c r="BU1" s="27"/>
-      <c r="BV1" s="27"/>
-      <c r="BW1" s="27"/>
-      <c r="BX1" s="27"/>
-      <c r="BY1" s="27"/>
-      <c r="BZ1" s="27"/>
-      <c r="CA1" s="27"/>
-      <c r="CB1" s="27"/>
-      <c r="CC1" s="27"/>
-      <c r="CD1" s="27"/>
-      <c r="CE1" s="27"/>
-      <c r="CF1" s="27"/>
-      <c r="CG1" s="27"/>
-    </row>
-    <row r="2" spans="1:85" s="26" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="84" t="str">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="34"/>
+    </row>
+    <row r="2" spans="1:11" s="40" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="77" t="str">
         <f ca="1">"Planning Area: "&amp;IFERROR(_xlfn.SINGLE(SOP_Planning_Area),"Offline")&amp;" | User: "&amp;_xlfn.SINGLE(_xll.IBPUser())</f>
         <v>Planning Area: Planning area | User: #Error, no current connection.</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="43"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="43"/>
-      <c r="AA2" s="43"/>
-      <c r="AB2" s="24"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="25"/>
-      <c r="AH2" s="25"/>
-      <c r="AI2" s="25"/>
-      <c r="AJ2" s="25"/>
-      <c r="AK2" s="25"/>
-      <c r="BR2" s="27"/>
-      <c r="BS2" s="27"/>
-      <c r="BT2" s="27"/>
-      <c r="BU2" s="27"/>
-      <c r="BV2" s="27"/>
-      <c r="BW2" s="27"/>
-      <c r="BX2" s="27"/>
-      <c r="BY2" s="27"/>
-      <c r="BZ2" s="27"/>
-      <c r="CA2" s="27"/>
-      <c r="CB2" s="27"/>
-      <c r="CC2" s="27"/>
-      <c r="CD2" s="27"/>
-      <c r="CE2" s="27"/>
-      <c r="CF2" s="27"/>
-      <c r="CG2" s="27"/>
-    </row>
-    <row r="3" spans="1:85" s="26" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="84" t="str" cm="1">
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="34"/>
+    </row>
+    <row r="3" spans="1:11" s="40" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="77" t="str" cm="1">
         <f t="array" ref="A3">"Last Refresh: "&amp;IFERROR(YEAR(SOP_Refresh_Timestamp)&amp;"-"&amp;TEXT(SOP_Refresh_Timestamp,"MMM")&amp;"-"&amp;DAY(SOP_Refresh_Timestamp)&amp;" "&amp;TEXT(SOP_Refresh_Timestamp,"HH:MM:SS"),"Offline")&amp;" | UoM: "&amp;IFERROR(SOP_TargetUoM,"(None)")&amp;" | Currency: "&amp;IFERROR(SOP_TargetCurrency,"(None)")</f>
         <v>Last Refresh: 1900-Jan-0 00:00:00 | UoM: (None) | Currency: (None)</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="43"/>
-      <c r="AA3" s="43"/>
-      <c r="AB3" s="24"/>
-      <c r="AC3" s="24"/>
-      <c r="AD3" s="24"/>
-      <c r="AE3" s="25"/>
-      <c r="AF3" s="25"/>
-      <c r="AG3" s="25"/>
-      <c r="AH3" s="25"/>
-      <c r="AI3" s="25"/>
-      <c r="AJ3" s="25"/>
-      <c r="AK3" s="25"/>
-      <c r="BR3" s="27"/>
-      <c r="BS3" s="27"/>
-      <c r="BT3" s="27"/>
-      <c r="BU3" s="27"/>
-      <c r="BV3" s="27"/>
-      <c r="BW3" s="27"/>
-      <c r="BX3" s="27"/>
-      <c r="BY3" s="27"/>
-      <c r="BZ3" s="27"/>
-      <c r="CA3" s="27"/>
-      <c r="CB3" s="27"/>
-      <c r="CC3" s="27"/>
-      <c r="CD3" s="27"/>
-      <c r="CE3" s="27"/>
-      <c r="CF3" s="27"/>
-      <c r="CG3" s="27"/>
-    </row>
-    <row r="4" spans="1:85" s="26" customFormat="1" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="43"/>
-      <c r="T4" s="43"/>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="43"/>
-      <c r="X4" s="43"/>
-      <c r="Y4" s="43"/>
-      <c r="Z4" s="43"/>
-      <c r="AA4" s="43"/>
-      <c r="AB4" s="24"/>
-      <c r="AC4" s="24"/>
-      <c r="AD4" s="24"/>
-      <c r="AE4" s="25"/>
-      <c r="AF4" s="25"/>
-      <c r="AG4" s="25"/>
-      <c r="AH4" s="25"/>
-      <c r="AI4" s="25"/>
-      <c r="AJ4" s="25"/>
-      <c r="AK4" s="25"/>
-      <c r="BR4" s="27"/>
-      <c r="BS4" s="27"/>
-      <c r="BT4" s="27"/>
-      <c r="BU4" s="27"/>
-      <c r="BV4" s="27"/>
-      <c r="BW4" s="27"/>
-      <c r="BX4" s="27"/>
-      <c r="BY4" s="27"/>
-      <c r="BZ4" s="27"/>
-      <c r="CA4" s="27"/>
-      <c r="CB4" s="27"/>
-      <c r="CC4" s="27"/>
-      <c r="CD4" s="27"/>
-      <c r="CE4" s="27"/>
-      <c r="CF4" s="27"/>
-      <c r="CG4" s="27"/>
-    </row>
-    <row r="5" spans="1:85" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="str">
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="34"/>
+    </row>
+    <row r="4" spans="1:11" s="40" customFormat="1" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="34"/>
+    </row>
+    <row r="5" spans="1:11" s="26" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="str">
         <f>SOP_Heading10</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="B5" s="28" t="str">
+      <c r="B5" s="24" t="str">
         <f>SOP_Heading9</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C5" s="28" t="str">
+      <c r="C5" s="24" t="str">
         <f>SOP_Heading8</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D5" s="28" t="str">
+      <c r="D5" s="24" t="str">
         <f>SOP_Heading7</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E5" s="28" t="str">
+      <c r="E5" s="24" t="str">
         <f>SOP_Heading6</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="F5" s="28" t="str">
+      <c r="F5" s="24" t="str">
         <f>SOP_Heading5</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G5" s="28" t="str">
+      <c r="G5" s="24" t="str">
         <f>SOP_Heading4</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H5" s="28" t="str">
+      <c r="H5" s="24" t="str">
         <f>SOP_Heading3</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I5" s="28" t="str">
+      <c r="I5" s="24" t="str">
         <f>SOP_Heading2</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J5" s="28" t="str">
+      <c r="J5" s="24" t="str">
         <f>SOP_Heading1</f>
         <v>Key Figure</v>
       </c>
-      <c r="K5" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="29"/>
-      <c r="AC5" s="29"/>
-      <c r="AD5" s="29"/>
-    </row>
-    <row r="6" spans="1:85" x14ac:dyDescent="0.25">
-      <c r="J6" s="47" t="s">
-        <v>24</v>
+      <c r="K5" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="J6" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -9433,15 +9528,16 @@
   <pageSetup orientation="portrait" horizontalDpi="300" r:id="rId1"/>
   <customProperties>
     <customPr name="EpmWorksheetKeyString_GUID" r:id="rId2"/>
+    <customPr name="IbpWorksheetKeyString_GUID" r:id="rId3"/>
   </customProperties>
-  <drawing r:id="rId3"/>
-  <legacyDrawing r:id="rId4"/>
-  <picture r:id="rId5"/>
+  <drawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
+  <picture r:id="rId6"/>
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="3093" r:id="rId6" name="FPMExcelClientSheetOptionstb1">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
+        <control shapeId="3093" r:id="rId7" name="FPMExcelClientSheetOptionstb1">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId8">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -9460,7 +9556,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="3093" r:id="rId6" name="FPMExcelClientSheetOptionstb1"/>
+        <control shapeId="3093" r:id="rId7" name="FPMExcelClientSheetOptionstb1"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -9470,311 +9566,125 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:CG6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
     <col min="2" max="9" width="1.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="23" width="13.42578125" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1"/>
+    <col min="12" max="23" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:85" s="26" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="82" t="str">
+    <row r="1" spans="1:11" s="40" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="75" t="str">
         <f>" IBP | " &amp;IFERROR(IF(SOP_Favorite_Name&lt;&gt;" ",SOP_Favorite_Name,IF(SOP_Template_Name&lt;&gt;" ",SOP_Template_Name,"Ad Hoc Planning View")),"Offline")</f>
         <v xml:space="preserve"> IBP | Ad Hoc Planning View</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="42"/>
-      <c r="W1" s="42"/>
-      <c r="X1" s="42"/>
-      <c r="Y1" s="42"/>
-      <c r="Z1" s="42"/>
-      <c r="AA1" s="42"/>
-      <c r="AB1" s="42"/>
-      <c r="AC1" s="24"/>
-      <c r="AD1" s="24"/>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="25"/>
-      <c r="AH1" s="25"/>
-      <c r="AI1" s="25"/>
-      <c r="AJ1" s="25"/>
-      <c r="AK1" s="25"/>
-      <c r="BR1" s="27"/>
-      <c r="BS1" s="27"/>
-      <c r="BT1" s="27"/>
-      <c r="BU1" s="27"/>
-      <c r="BV1" s="27"/>
-      <c r="BW1" s="27"/>
-      <c r="BX1" s="27"/>
-      <c r="BY1" s="27"/>
-      <c r="BZ1" s="27"/>
-      <c r="CA1" s="27"/>
-      <c r="CB1" s="27"/>
-      <c r="CC1" s="27"/>
-      <c r="CD1" s="27"/>
-      <c r="CE1" s="27"/>
-      <c r="CF1" s="27"/>
-      <c r="CG1" s="27"/>
-    </row>
-    <row r="2" spans="1:85" s="26" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="84" t="str">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="33"/>
+    </row>
+    <row r="2" spans="1:11" s="40" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="77" t="str">
         <f ca="1">"Planning Area: "&amp;IFERROR(_xlfn.SINGLE(SOP_Planning_Area),"Offline")&amp;" | User: "&amp;_xlfn.SINGLE(_xll.IBPUser())</f>
         <v>Planning Area: Planning area | User: #Error, no current connection.</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
-      <c r="V2" s="42"/>
-      <c r="W2" s="42"/>
-      <c r="X2" s="42"/>
-      <c r="Y2" s="42"/>
-      <c r="Z2" s="42"/>
-      <c r="AA2" s="42"/>
-      <c r="AB2" s="42"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="25"/>
-      <c r="AH2" s="25"/>
-      <c r="AI2" s="25"/>
-      <c r="AJ2" s="25"/>
-      <c r="AK2" s="25"/>
-      <c r="BR2" s="27"/>
-      <c r="BS2" s="27"/>
-      <c r="BT2" s="27"/>
-      <c r="BU2" s="27"/>
-      <c r="BV2" s="27"/>
-      <c r="BW2" s="27"/>
-      <c r="BX2" s="27"/>
-      <c r="BY2" s="27"/>
-      <c r="BZ2" s="27"/>
-      <c r="CA2" s="27"/>
-      <c r="CB2" s="27"/>
-      <c r="CC2" s="27"/>
-      <c r="CD2" s="27"/>
-      <c r="CE2" s="27"/>
-      <c r="CF2" s="27"/>
-      <c r="CG2" s="27"/>
-    </row>
-    <row r="3" spans="1:85" s="26" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="84" t="str" cm="1">
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="33"/>
+    </row>
+    <row r="3" spans="1:11" s="40" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="77" t="str" cm="1">
         <f t="array" ref="A3">"Last Refresh: "&amp;IFERROR(YEAR(SOP_Refresh_Timestamp)&amp;"-"&amp;TEXT(SOP_Refresh_Timestamp,"MMM")&amp;"-"&amp;DAY(SOP_Refresh_Timestamp)&amp;" "&amp;TEXT(SOP_Refresh_Timestamp,"HH:MM:SS"),"Offline")&amp;" | UoM: "&amp;IFERROR(SOP_TargetUoM,"(None)")&amp;" | Currency: "&amp;IFERROR(SOP_TargetCurrency,"(None)")</f>
         <v>Last Refresh: 1900-Jan-0 00:00:00 | UoM: (None) | Currency: (None)</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="42"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="42"/>
-      <c r="U3" s="42"/>
-      <c r="V3" s="42"/>
-      <c r="W3" s="42"/>
-      <c r="X3" s="42"/>
-      <c r="Y3" s="42"/>
-      <c r="Z3" s="42"/>
-      <c r="AA3" s="42"/>
-      <c r="AB3" s="42"/>
-      <c r="AC3" s="24"/>
-      <c r="AD3" s="24"/>
-      <c r="AE3" s="25"/>
-      <c r="AF3" s="25"/>
-      <c r="AG3" s="25"/>
-      <c r="AH3" s="25"/>
-      <c r="AI3" s="25"/>
-      <c r="AJ3" s="25"/>
-      <c r="AK3" s="25"/>
-      <c r="BR3" s="27"/>
-      <c r="BS3" s="27"/>
-      <c r="BT3" s="27"/>
-      <c r="BU3" s="27"/>
-      <c r="BV3" s="27"/>
-      <c r="BW3" s="27"/>
-      <c r="BX3" s="27"/>
-      <c r="BY3" s="27"/>
-      <c r="BZ3" s="27"/>
-      <c r="CA3" s="27"/>
-      <c r="CB3" s="27"/>
-      <c r="CC3" s="27"/>
-      <c r="CD3" s="27"/>
-      <c r="CE3" s="27"/>
-      <c r="CF3" s="27"/>
-      <c r="CG3" s="27"/>
-    </row>
-    <row r="4" spans="1:85" s="26" customFormat="1" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="42"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="42"/>
-      <c r="S4" s="42"/>
-      <c r="T4" s="42"/>
-      <c r="U4" s="42"/>
-      <c r="V4" s="42"/>
-      <c r="W4" s="42"/>
-      <c r="X4" s="42"/>
-      <c r="Y4" s="42"/>
-      <c r="Z4" s="42"/>
-      <c r="AA4" s="42"/>
-      <c r="AB4" s="42"/>
-      <c r="AC4" s="24"/>
-      <c r="AD4" s="24"/>
-      <c r="AE4" s="25"/>
-      <c r="AF4" s="25"/>
-      <c r="AG4" s="25"/>
-      <c r="AH4" s="25"/>
-      <c r="AI4" s="25"/>
-      <c r="AJ4" s="25"/>
-      <c r="AK4" s="25"/>
-      <c r="BR4" s="27"/>
-      <c r="BS4" s="27"/>
-      <c r="BT4" s="27"/>
-      <c r="BU4" s="27"/>
-      <c r="BV4" s="27"/>
-      <c r="BW4" s="27"/>
-      <c r="BX4" s="27"/>
-      <c r="BY4" s="27"/>
-      <c r="BZ4" s="27"/>
-      <c r="CA4" s="27"/>
-      <c r="CB4" s="27"/>
-      <c r="CC4" s="27"/>
-      <c r="CD4" s="27"/>
-      <c r="CE4" s="27"/>
-      <c r="CF4" s="27"/>
-      <c r="CG4" s="27"/>
-    </row>
-    <row r="5" spans="1:85" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="str">
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="33"/>
+    </row>
+    <row r="4" spans="1:11" s="40" customFormat="1" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="33"/>
+    </row>
+    <row r="5" spans="1:11" s="26" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="str">
         <f>SOP_Heading10</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="B5" s="28" t="str">
+      <c r="B5" s="24" t="str">
         <f>SOP_Heading9</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C5" s="28" t="str">
+      <c r="C5" s="24" t="str">
         <f>SOP_Heading8</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="D5" s="28" t="str">
+      <c r="D5" s="24" t="str">
         <f>SOP_Heading7</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="E5" s="28" t="str">
+      <c r="E5" s="24" t="str">
         <f>SOP_Heading6</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="F5" s="28" t="str">
+      <c r="F5" s="24" t="str">
         <f>SOP_Heading5</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G5" s="28" t="str">
+      <c r="G5" s="24" t="str">
         <f>SOP_Heading4</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H5" s="28" t="str">
+      <c r="H5" s="24" t="str">
         <f>SOP_Heading3</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="I5" s="28" t="str">
+      <c r="I5" s="24" t="str">
         <f>SOP_Heading2</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J5" s="28" t="str">
+      <c r="J5" s="24" t="str">
         <f>SOP_Heading1</f>
         <v>Key Figure</v>
       </c>
-      <c r="K5" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="29"/>
-      <c r="AC5" s="29"/>
-      <c r="AD5" s="29"/>
-    </row>
-    <row r="6" spans="1:85" x14ac:dyDescent="0.25">
-      <c r="J6" s="47" t="s">
-        <v>24</v>
+      <c r="K5" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="J6" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -9794,8 +9704,33 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="5121" r:id="rId6" name="FPMExcelClientSheetOptionstb1">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId7">
+        <control shapeId="5127" r:id="rId6" name="TextBox2">
+          <controlPr defaultSize="0" disabled="1" autoLine="0" r:id="rId7">
+            <anchor>
+              <from>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>76200</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>85725</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>9525</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="5127" r:id="rId6" name="TextBox2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="5121" r:id="rId8" name="FPMExcelClientSheetOptionstb1">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -9814,32 +9749,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="5121" r:id="rId6" name="FPMExcelClientSheetOptionstb1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="5127" r:id="rId8" name="TextBox2">
-          <controlPr defaultSize="0" disabled="1" autoLine="0" r:id="rId9">
-            <anchor>
-              <from>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>76200</xdr:colOff>
-                <xdr:row>5</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>85725</xdr:colOff>
-                <xdr:row>5</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="5127" r:id="rId8" name="TextBox2"/>
+        <control shapeId="5121" r:id="rId8" name="FPMExcelClientSheetOptionstb1"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
@@ -9848,6 +9758,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
+  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" removed="0"/>
 </clbl:labelList>
 </file>
--- a/Template_Without_VBA/TemplateWithoutVBA.xlsx
+++ b/Template_Without_VBA/TemplateWithoutVBA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\I519576\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\I334271\OneDrive - SAP SE\Shares\New templates to share\Work files without VBA template\Upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37241434-039C-4692-AA01-DF631EA1AD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A776317C-85BD-4809-A56C-C15B2DFBD53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="374" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -566,14 +566,12 @@
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <family val="2"/>
-      <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="238"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1149,32 +1147,7 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1185,10 +1158,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1205,12 +1174,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1221,12 +1206,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="5"/>
@@ -1279,18 +1277,6 @@
 
 <file path=xl/activeX/activeX3.xml><?xml version="1.0" encoding="utf-8"?>
 <ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D40-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX4.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D10-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX5.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D10-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/activeX/activeX6.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D10-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1605,7 +1591,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1691,7 +1677,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1777,7 +1763,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1863,7 +1849,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1949,7 +1935,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2092,7 +2078,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2178,7 +2164,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2264,7 +2250,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2350,7 +2336,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2436,7 +2422,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2522,7 +2508,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2608,7 +2594,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2694,7 +2680,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2763,7 +2749,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2850,7 +2836,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2936,7 +2922,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3022,7 +3008,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3108,7 +3094,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3194,7 +3180,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3263,7 +3249,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3407,7 +3393,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3493,7 +3479,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3579,7 +3565,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3665,7 +3651,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3751,7 +3737,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3837,7 +3823,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3923,7 +3909,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -3992,7 +3978,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4062,7 +4048,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4132,7 +4118,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4202,7 +4188,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4272,7 +4258,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4342,7 +4328,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4412,7 +4398,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4482,7 +4468,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4552,7 +4538,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4622,7 +4608,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4692,7 +4678,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4762,7 +4748,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4832,7 +4818,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4902,7 +4888,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -4972,7 +4958,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -5042,7 +5028,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -5129,7 +5115,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -5215,7 +5201,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -5301,7 +5287,7 @@
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-GB" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -5367,68 +5353,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>0</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>0</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3093" name="FPMExcelClientSheetOptionstb1" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s3093"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000150C0000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
@@ -5478,126 +5402,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor>
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>0</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>0</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5121" name="FPMExcelClientSheetOptionstb1" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5121"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000001140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="absolute">
-        <xdr:from>
-          <xdr:col>8</xdr:col>
-          <xdr:colOff>76200</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>8</xdr:col>
-          <xdr:colOff>85725</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5127" name="TextBox2" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5127"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000007140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
@@ -5913,19 +5717,19 @@
   <sheetData>
     <row r="1" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
     </row>
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
@@ -5975,43 +5779,43 @@
     </row>
     <row r="5" spans="1:17" ht="28.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="55"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="66"/>
       <c r="Q5" s="19" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="28.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
-      <c r="B6" s="56"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="58"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="74"/>
       <c r="Q6" s="20" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="63" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="15"/>
@@ -6024,13 +5828,13 @@
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
       <c r="L7" s="16"/>
-      <c r="Q7" s="62" t="s">
+      <c r="Q7" s="70" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
-      <c r="B8" s="60"/>
+      <c r="B8" s="53"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -6041,35 +5845,35 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="10"/>
-      <c r="Q8" s="62"/>
+      <c r="Q8" s="70"/>
     </row>
     <row r="9" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
-      <c r="B9" s="60"/>
+      <c r="B9" s="53"/>
       <c r="C9" s="5"/>
       <c r="D9" s="6"/>
-      <c r="E9" s="63" t="s">
+      <c r="E9" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="64"/>
-      <c r="G9" s="65"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="57"/>
       <c r="H9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="63" t="s">
+      <c r="I9" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="64"/>
-      <c r="K9" s="65"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="57"/>
       <c r="L9" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="Q9" s="62"/>
+      <c r="Q9" s="70"/>
     </row>
     <row r="10" spans="1:17" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="66"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="58"/>
       <c r="D10" s="2"/>
       <c r="E10" s="30"/>
       <c r="F10" s="30"/>
@@ -6079,12 +5883,12 @@
       <c r="J10" s="30"/>
       <c r="K10" s="30"/>
       <c r="L10" s="10"/>
-      <c r="Q10" s="62"/>
+      <c r="Q10" s="70"/>
     </row>
     <row r="11" spans="1:17" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="67"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="59"/>
       <c r="D11" s="31" t="s">
         <v>11</v>
       </c>
@@ -6104,12 +5908,12 @@
       <c r="L11" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="Q11" s="62"/>
+      <c r="Q11" s="70"/>
     </row>
     <row r="12" spans="1:17" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
-      <c r="B12" s="61"/>
-      <c r="C12" s="68"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="61"/>
       <c r="D12" s="13"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
@@ -6119,11 +5923,11 @@
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
       <c r="L12" s="14"/>
-      <c r="Q12" s="62"/>
+      <c r="Q12" s="70"/>
     </row>
     <row r="13" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="52" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="2"/>
@@ -6136,11 +5940,11 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="10"/>
-      <c r="Q13" s="62"/>
+      <c r="Q13" s="70"/>
     </row>
     <row r="14" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
-      <c r="B14" s="60"/>
+      <c r="B14" s="53"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -6151,35 +5955,35 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="10"/>
-      <c r="Q14" s="62"/>
+      <c r="Q14" s="70"/>
     </row>
     <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
-      <c r="B15" s="60"/>
+      <c r="B15" s="53"/>
       <c r="C15" s="5"/>
       <c r="D15" s="6"/>
-      <c r="E15" s="63" t="s">
+      <c r="E15" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="65"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="57"/>
       <c r="H15" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I15" s="63" t="s">
+      <c r="I15" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="J15" s="64"/>
-      <c r="K15" s="65"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="57"/>
       <c r="L15" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="Q15" s="62"/>
+      <c r="Q15" s="70"/>
     </row>
     <row r="16" spans="1:17" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
-      <c r="B16" s="60"/>
-      <c r="C16" s="66"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="58"/>
       <c r="D16" s="2"/>
       <c r="E16" s="30"/>
       <c r="F16" s="30"/>
@@ -6189,12 +5993,12 @@
       <c r="J16" s="30"/>
       <c r="K16" s="30"/>
       <c r="L16" s="10"/>
-      <c r="Q16" s="62"/>
+      <c r="Q16" s="70"/>
     </row>
     <row r="17" spans="1:17" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="67"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="59"/>
       <c r="D17" s="31" t="s">
         <v>11</v>
       </c>
@@ -6214,12 +6018,12 @@
       <c r="L17" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="Q17" s="62"/>
+      <c r="Q17" s="70"/>
     </row>
     <row r="18" spans="1:17" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
-      <c r="B18" s="61"/>
-      <c r="C18" s="68"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="13"/>
       <c r="E18" s="18"/>
       <c r="F18" s="18"/>
@@ -6229,7 +6033,7 @@
       <c r="J18" s="18"/>
       <c r="K18" s="18"/>
       <c r="L18" s="14"/>
-      <c r="Q18" s="62"/>
+      <c r="Q18" s="70"/>
     </row>
     <row r="19" spans="1:17" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
@@ -6244,7 +6048,7 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
-      <c r="Q19" s="62"/>
+      <c r="Q19" s="70"/>
     </row>
     <row r="20" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
@@ -6263,43 +6067,43 @@
     </row>
     <row r="21" spans="1:17" ht="28.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
-      <c r="B21" s="53" t="s">
+      <c r="B21" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="55"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="66"/>
       <c r="Q21" s="22" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
-      <c r="B22" s="70"/>
-      <c r="C22" s="71"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="71"/>
-      <c r="K22" s="71"/>
-      <c r="L22" s="72"/>
-      <c r="Q22" s="62" t="s">
+      <c r="B22" s="67"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="69"/>
+      <c r="Q22" s="70" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
-      <c r="B23" s="69" t="s">
+      <c r="B23" s="52" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="2"/>
@@ -6312,35 +6116,35 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="10"/>
-      <c r="Q23" s="62"/>
+      <c r="Q23" s="70"/>
     </row>
     <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
-      <c r="B24" s="60"/>
+      <c r="B24" s="53"/>
       <c r="C24" s="5"/>
       <c r="D24" s="6"/>
-      <c r="E24" s="63" t="s">
+      <c r="E24" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="64"/>
-      <c r="G24" s="65"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="57"/>
       <c r="H24" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I24" s="63" t="s">
+      <c r="I24" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="J24" s="64"/>
-      <c r="K24" s="65"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="57"/>
       <c r="L24" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="Q24" s="62"/>
+      <c r="Q24" s="70"/>
     </row>
     <row r="25" spans="1:17" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
-      <c r="B25" s="60"/>
-      <c r="C25" s="66"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="58"/>
       <c r="D25" s="2"/>
       <c r="E25" s="30"/>
       <c r="F25" s="30"/>
@@ -6350,12 +6154,12 @@
       <c r="J25" s="30"/>
       <c r="K25" s="30"/>
       <c r="L25" s="10"/>
-      <c r="Q25" s="62"/>
+      <c r="Q25" s="70"/>
     </row>
     <row r="26" spans="1:17" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
-      <c r="B26" s="60"/>
-      <c r="C26" s="67"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="59"/>
       <c r="D26" s="31" t="s">
         <v>19</v>
       </c>
@@ -6375,12 +6179,12 @@
       <c r="L26" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="Q26" s="62"/>
+      <c r="Q26" s="70"/>
     </row>
     <row r="27" spans="1:17" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
-      <c r="B27" s="60"/>
-      <c r="C27" s="73"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="60"/>
       <c r="D27" s="37"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
@@ -6390,12 +6194,12 @@
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
       <c r="L27" s="38"/>
-      <c r="Q27" s="62"/>
+      <c r="Q27" s="70"/>
     </row>
     <row r="28" spans="1:17" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
-      <c r="B28" s="60"/>
-      <c r="C28" s="67"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="59"/>
       <c r="D28" s="2"/>
       <c r="E28" s="30"/>
       <c r="F28" s="30"/>
@@ -6405,12 +6209,12 @@
       <c r="J28" s="30"/>
       <c r="K28" s="30"/>
       <c r="L28" s="10"/>
-      <c r="Q28" s="62"/>
+      <c r="Q28" s="70"/>
     </row>
     <row r="29" spans="1:17" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
-      <c r="B29" s="60"/>
-      <c r="C29" s="67"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="59"/>
       <c r="D29" s="31" t="s">
         <v>20</v>
       </c>
@@ -6430,12 +6234,12 @@
       <c r="L29" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="Q29" s="62"/>
+      <c r="Q29" s="70"/>
     </row>
     <row r="30" spans="1:17" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
-      <c r="B30" s="60"/>
-      <c r="C30" s="73"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="60"/>
       <c r="D30" s="37"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
@@ -6449,8 +6253,8 @@
     </row>
     <row r="31" spans="1:17" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
-      <c r="B31" s="60"/>
-      <c r="C31" s="67"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="59"/>
       <c r="D31" s="2"/>
       <c r="E31" s="30"/>
       <c r="F31" s="30"/>
@@ -6463,8 +6267,8 @@
     </row>
     <row r="32" spans="1:17" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
-      <c r="B32" s="60"/>
-      <c r="C32" s="67"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="59"/>
       <c r="D32" s="31" t="s">
         <v>22</v>
       </c>
@@ -6487,8 +6291,8 @@
     </row>
     <row r="33" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
-      <c r="B33" s="60"/>
-      <c r="C33" s="73"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="60"/>
       <c r="D33" s="37"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
@@ -6501,8 +6305,8 @@
     </row>
     <row r="34" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
-      <c r="B34" s="60"/>
-      <c r="C34" s="67"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="59"/>
       <c r="D34" s="2"/>
       <c r="E34" s="30"/>
       <c r="F34" s="30"/>
@@ -6515,8 +6319,8 @@
     </row>
     <row r="35" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
-      <c r="B35" s="60"/>
-      <c r="C35" s="67"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="59"/>
       <c r="D35" s="31" t="s">
         <v>23</v>
       </c>
@@ -6539,8 +6343,8 @@
     </row>
     <row r="36" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
-      <c r="B36" s="60"/>
-      <c r="C36" s="73"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="60"/>
       <c r="D36" s="37"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
@@ -6553,8 +6357,8 @@
     </row>
     <row r="37" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
-      <c r="B37" s="60"/>
-      <c r="C37" s="67"/>
+      <c r="B37" s="53"/>
+      <c r="C37" s="59"/>
       <c r="D37" s="2"/>
       <c r="E37" s="30"/>
       <c r="F37" s="30"/>
@@ -6567,8 +6371,8 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
-      <c r="B38" s="60"/>
-      <c r="C38" s="67"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="59"/>
       <c r="D38" s="31" t="s">
         <v>25</v>
       </c>
@@ -6583,7 +6387,7 @@
     </row>
     <row r="39" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
-      <c r="B39" s="60"/>
+      <c r="B39" s="53"/>
       <c r="C39" s="35"/>
       <c r="D39" s="31"/>
       <c r="E39" s="30"/>
@@ -6597,7 +6401,7 @@
     </row>
     <row r="40" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
-      <c r="B40" s="60"/>
+      <c r="B40" s="53"/>
       <c r="C40" s="35"/>
       <c r="D40" s="32" t="s">
         <v>26</v>
@@ -6621,7 +6425,7 @@
     </row>
     <row r="41" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
-      <c r="B41" s="60"/>
+      <c r="B41" s="53"/>
       <c r="C41" s="35"/>
       <c r="D41" s="27"/>
       <c r="E41" s="7"/>
@@ -6635,7 +6439,7 @@
     </row>
     <row r="42" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
-      <c r="B42" s="60"/>
+      <c r="B42" s="53"/>
       <c r="C42" s="35"/>
       <c r="D42" s="31"/>
       <c r="E42" s="30"/>
@@ -6649,7 +6453,7 @@
     </row>
     <row r="43" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
-      <c r="B43" s="60"/>
+      <c r="B43" s="53"/>
       <c r="C43" s="35"/>
       <c r="D43" s="32" t="s">
         <v>28</v>
@@ -6673,7 +6477,7 @@
     </row>
     <row r="44" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
-      <c r="B44" s="60"/>
+      <c r="B44" s="53"/>
       <c r="C44" s="35"/>
       <c r="D44" s="27"/>
       <c r="E44" s="7"/>
@@ -6687,7 +6491,7 @@
     </row>
     <row r="45" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
-      <c r="B45" s="60"/>
+      <c r="B45" s="53"/>
       <c r="C45" s="35"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -6701,7 +6505,7 @@
     </row>
     <row r="46" spans="1:12" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
-      <c r="B46" s="61"/>
+      <c r="B46" s="54"/>
       <c r="C46" s="36"/>
       <c r="D46" s="13"/>
       <c r="E46" s="13"/>
@@ -6715,7 +6519,7 @@
     </row>
     <row r="47" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
-      <c r="B47" s="59" t="s">
+      <c r="B47" s="63" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="15"/>
@@ -6731,30 +6535,30 @@
     </row>
     <row r="48" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
-      <c r="B48" s="60"/>
+      <c r="B48" s="53"/>
       <c r="C48" s="5"/>
       <c r="D48" s="6"/>
-      <c r="E48" s="63" t="s">
+      <c r="E48" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="F48" s="64"/>
-      <c r="G48" s="65"/>
+      <c r="F48" s="56"/>
+      <c r="G48" s="57"/>
       <c r="H48" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I48" s="63" t="s">
+      <c r="I48" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="J48" s="64"/>
-      <c r="K48" s="65"/>
+      <c r="J48" s="56"/>
+      <c r="K48" s="57"/>
       <c r="L48" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
-      <c r="B49" s="60"/>
-      <c r="C49" s="66"/>
+      <c r="B49" s="53"/>
+      <c r="C49" s="58"/>
       <c r="D49" s="2"/>
       <c r="E49" s="30"/>
       <c r="F49" s="30"/>
@@ -6767,8 +6571,8 @@
     </row>
     <row r="50" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
-      <c r="B50" s="60"/>
-      <c r="C50" s="67"/>
+      <c r="B50" s="53"/>
+      <c r="C50" s="59"/>
       <c r="D50" s="31" t="s">
         <v>19</v>
       </c>
@@ -6791,8 +6595,8 @@
     </row>
     <row r="51" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
-      <c r="B51" s="60"/>
-      <c r="C51" s="73"/>
+      <c r="B51" s="53"/>
+      <c r="C51" s="60"/>
       <c r="D51" s="37"/>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
@@ -6805,8 +6609,8 @@
     </row>
     <row r="52" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
-      <c r="B52" s="60"/>
-      <c r="C52" s="67"/>
+      <c r="B52" s="53"/>
+      <c r="C52" s="59"/>
       <c r="D52" s="2"/>
       <c r="E52" s="30"/>
       <c r="F52" s="30"/>
@@ -6819,8 +6623,8 @@
     </row>
     <row r="53" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
-      <c r="B53" s="60"/>
-      <c r="C53" s="67"/>
+      <c r="B53" s="53"/>
+      <c r="C53" s="59"/>
       <c r="D53" s="31" t="s">
         <v>20</v>
       </c>
@@ -6843,8 +6647,8 @@
     </row>
     <row r="54" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
-      <c r="B54" s="60"/>
-      <c r="C54" s="73"/>
+      <c r="B54" s="53"/>
+      <c r="C54" s="60"/>
       <c r="D54" s="37"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
@@ -6857,8 +6661,8 @@
     </row>
     <row r="55" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
-      <c r="B55" s="60"/>
-      <c r="C55" s="67"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="59"/>
       <c r="D55" s="2"/>
       <c r="E55" s="30"/>
       <c r="F55" s="30"/>
@@ -6871,8 +6675,8 @@
     </row>
     <row r="56" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
-      <c r="B56" s="60"/>
-      <c r="C56" s="67"/>
+      <c r="B56" s="53"/>
+      <c r="C56" s="59"/>
       <c r="D56" s="31" t="s">
         <v>22</v>
       </c>
@@ -6895,8 +6699,8 @@
     </row>
     <row r="57" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
-      <c r="B57" s="60"/>
-      <c r="C57" s="73"/>
+      <c r="B57" s="53"/>
+      <c r="C57" s="60"/>
       <c r="D57" s="37"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
@@ -6909,8 +6713,8 @@
     </row>
     <row r="58" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
-      <c r="B58" s="60"/>
-      <c r="C58" s="67"/>
+      <c r="B58" s="53"/>
+      <c r="C58" s="59"/>
       <c r="D58" s="2"/>
       <c r="E58" s="30"/>
       <c r="F58" s="30"/>
@@ -6923,8 +6727,8 @@
     </row>
     <row r="59" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
-      <c r="B59" s="60"/>
-      <c r="C59" s="67"/>
+      <c r="B59" s="53"/>
+      <c r="C59" s="59"/>
       <c r="D59" s="31" t="s">
         <v>23</v>
       </c>
@@ -6947,8 +6751,8 @@
     </row>
     <row r="60" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
-      <c r="B60" s="60"/>
-      <c r="C60" s="73"/>
+      <c r="B60" s="53"/>
+      <c r="C60" s="60"/>
       <c r="D60" s="37"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
@@ -6961,8 +6765,8 @@
     </row>
     <row r="61" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
-      <c r="B61" s="60"/>
-      <c r="C61" s="67"/>
+      <c r="B61" s="53"/>
+      <c r="C61" s="59"/>
       <c r="D61" s="2"/>
       <c r="E61" s="30"/>
       <c r="F61" s="30"/>
@@ -6975,8 +6779,8 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
-      <c r="B62" s="60"/>
-      <c r="C62" s="67"/>
+      <c r="B62" s="53"/>
+      <c r="C62" s="59"/>
       <c r="D62" s="31" t="s">
         <v>25</v>
       </c>
@@ -6991,7 +6795,7 @@
     </row>
     <row r="63" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
-      <c r="B63" s="60"/>
+      <c r="B63" s="53"/>
       <c r="C63" s="35"/>
       <c r="D63" s="31"/>
       <c r="E63" s="30"/>
@@ -7005,7 +6809,7 @@
     </row>
     <row r="64" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
-      <c r="B64" s="60"/>
+      <c r="B64" s="53"/>
       <c r="C64" s="35"/>
       <c r="D64" s="32" t="s">
         <v>26</v>
@@ -7029,7 +6833,7 @@
     </row>
     <row r="65" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
-      <c r="B65" s="60"/>
+      <c r="B65" s="53"/>
       <c r="C65" s="35"/>
       <c r="D65" s="27"/>
       <c r="E65" s="7"/>
@@ -7043,7 +6847,7 @@
     </row>
     <row r="66" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
-      <c r="B66" s="60"/>
+      <c r="B66" s="53"/>
       <c r="C66" s="35"/>
       <c r="D66" s="31"/>
       <c r="E66" s="30"/>
@@ -7057,7 +6861,7 @@
     </row>
     <row r="67" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
-      <c r="B67" s="60"/>
+      <c r="B67" s="53"/>
       <c r="C67" s="35"/>
       <c r="D67" s="32" t="s">
         <v>30</v>
@@ -7081,7 +6885,7 @@
     </row>
     <row r="68" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
-      <c r="B68" s="60"/>
+      <c r="B68" s="53"/>
       <c r="C68" s="35"/>
       <c r="D68" s="27"/>
       <c r="E68" s="7"/>
@@ -7095,7 +6899,7 @@
     </row>
     <row r="69" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
-      <c r="B69" s="60"/>
+      <c r="B69" s="53"/>
       <c r="C69" s="35"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
@@ -7109,7 +6913,7 @@
     </row>
     <row r="70" spans="1:12" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
-      <c r="B70" s="61"/>
+      <c r="B70" s="54"/>
       <c r="C70" s="36"/>
       <c r="D70" s="13"/>
       <c r="E70" s="13"/>
@@ -7151,37 +6955,37 @@
     </row>
     <row r="73" spans="1:12" ht="28.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
-      <c r="B73" s="53" t="s">
+      <c r="B73" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="C73" s="54"/>
-      <c r="D73" s="54"/>
-      <c r="E73" s="54"/>
-      <c r="F73" s="54"/>
-      <c r="G73" s="54"/>
-      <c r="H73" s="54"/>
-      <c r="I73" s="54"/>
-      <c r="J73" s="54"/>
-      <c r="K73" s="54"/>
-      <c r="L73" s="55"/>
+      <c r="C73" s="65"/>
+      <c r="D73" s="65"/>
+      <c r="E73" s="65"/>
+      <c r="F73" s="65"/>
+      <c r="G73" s="65"/>
+      <c r="H73" s="65"/>
+      <c r="I73" s="65"/>
+      <c r="J73" s="65"/>
+      <c r="K73" s="65"/>
+      <c r="L73" s="66"/>
     </row>
     <row r="74" spans="1:12" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
-      <c r="B74" s="70"/>
-      <c r="C74" s="71"/>
-      <c r="D74" s="71"/>
-      <c r="E74" s="71"/>
-      <c r="F74" s="71"/>
-      <c r="G74" s="71"/>
-      <c r="H74" s="71"/>
-      <c r="I74" s="71"/>
-      <c r="J74" s="71"/>
-      <c r="K74" s="71"/>
-      <c r="L74" s="72"/>
+      <c r="B74" s="67"/>
+      <c r="C74" s="68"/>
+      <c r="D74" s="68"/>
+      <c r="E74" s="68"/>
+      <c r="F74" s="68"/>
+      <c r="G74" s="68"/>
+      <c r="H74" s="68"/>
+      <c r="I74" s="68"/>
+      <c r="J74" s="68"/>
+      <c r="K74" s="68"/>
+      <c r="L74" s="69"/>
     </row>
     <row r="75" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
-      <c r="B75" s="69" t="s">
+      <c r="B75" s="52" t="s">
         <v>15</v>
       </c>
       <c r="C75" s="2"/>
@@ -7197,30 +7001,30 @@
     </row>
     <row r="76" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
-      <c r="B76" s="60"/>
+      <c r="B76" s="53"/>
       <c r="C76" s="5"/>
       <c r="D76" s="6"/>
-      <c r="E76" s="63" t="s">
+      <c r="E76" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="F76" s="64"/>
-      <c r="G76" s="65"/>
+      <c r="F76" s="56"/>
+      <c r="G76" s="57"/>
       <c r="H76" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I76" s="63" t="s">
+      <c r="I76" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="J76" s="64"/>
-      <c r="K76" s="65"/>
+      <c r="J76" s="56"/>
+      <c r="K76" s="57"/>
       <c r="L76" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
-      <c r="B77" s="60"/>
-      <c r="C77" s="66"/>
+      <c r="B77" s="53"/>
+      <c r="C77" s="58"/>
       <c r="D77" s="2"/>
       <c r="E77" s="30"/>
       <c r="F77" s="30"/>
@@ -7233,8 +7037,8 @@
     </row>
     <row r="78" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
-      <c r="B78" s="60"/>
-      <c r="C78" s="67"/>
+      <c r="B78" s="53"/>
+      <c r="C78" s="59"/>
       <c r="D78" s="31" t="s">
         <v>33</v>
       </c>
@@ -7257,8 +7061,8 @@
     </row>
     <row r="79" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
-      <c r="B79" s="60"/>
-      <c r="C79" s="73"/>
+      <c r="B79" s="53"/>
+      <c r="C79" s="60"/>
       <c r="D79" s="37"/>
       <c r="E79" s="7"/>
       <c r="F79" s="7"/>
@@ -7271,8 +7075,8 @@
     </row>
     <row r="80" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
-      <c r="B80" s="60"/>
-      <c r="C80" s="67"/>
+      <c r="B80" s="53"/>
+      <c r="C80" s="59"/>
       <c r="D80" s="2"/>
       <c r="E80" s="30"/>
       <c r="F80" s="30"/>
@@ -7285,8 +7089,8 @@
     </row>
     <row r="81" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
-      <c r="B81" s="60"/>
-      <c r="C81" s="67"/>
+      <c r="B81" s="53"/>
+      <c r="C81" s="59"/>
       <c r="D81" s="31" t="s">
         <v>34</v>
       </c>
@@ -7309,8 +7113,8 @@
     </row>
     <row r="82" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
-      <c r="B82" s="74"/>
-      <c r="C82" s="73"/>
+      <c r="B82" s="62"/>
+      <c r="C82" s="60"/>
       <c r="D82" s="37"/>
       <c r="E82" s="7"/>
       <c r="F82" s="7"/>
@@ -7323,7 +7127,7 @@
     </row>
     <row r="83" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
-      <c r="B83" s="69" t="s">
+      <c r="B83" s="52" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="2"/>
@@ -7339,30 +7143,30 @@
     </row>
     <row r="84" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
-      <c r="B84" s="60"/>
+      <c r="B84" s="53"/>
       <c r="C84" s="5"/>
       <c r="D84" s="6"/>
-      <c r="E84" s="63" t="s">
+      <c r="E84" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="F84" s="64"/>
-      <c r="G84" s="65"/>
+      <c r="F84" s="56"/>
+      <c r="G84" s="57"/>
       <c r="H84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I84" s="63" t="s">
+      <c r="I84" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="J84" s="64"/>
-      <c r="K84" s="65"/>
+      <c r="J84" s="56"/>
+      <c r="K84" s="57"/>
       <c r="L84" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
-      <c r="B85" s="60"/>
-      <c r="C85" s="66"/>
+      <c r="B85" s="53"/>
+      <c r="C85" s="58"/>
       <c r="D85" s="2"/>
       <c r="E85" s="30"/>
       <c r="F85" s="30"/>
@@ -7375,8 +7179,8 @@
     </row>
     <row r="86" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
-      <c r="B86" s="60"/>
-      <c r="C86" s="67"/>
+      <c r="B86" s="53"/>
+      <c r="C86" s="59"/>
       <c r="D86" s="31" t="s">
         <v>33</v>
       </c>
@@ -7399,8 +7203,8 @@
     </row>
     <row r="87" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
-      <c r="B87" s="60"/>
-      <c r="C87" s="73"/>
+      <c r="B87" s="53"/>
+      <c r="C87" s="60"/>
       <c r="D87" s="37"/>
       <c r="E87" s="7"/>
       <c r="F87" s="7"/>
@@ -7413,8 +7217,8 @@
     </row>
     <row r="88" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
-      <c r="B88" s="60"/>
-      <c r="C88" s="67"/>
+      <c r="B88" s="53"/>
+      <c r="C88" s="59"/>
       <c r="D88" s="2"/>
       <c r="E88" s="30"/>
       <c r="F88" s="30"/>
@@ -7427,8 +7231,8 @@
     </row>
     <row r="89" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
-      <c r="B89" s="60"/>
-      <c r="C89" s="67"/>
+      <c r="B89" s="53"/>
+      <c r="C89" s="59"/>
       <c r="D89" s="31" t="s">
         <v>34</v>
       </c>
@@ -7451,8 +7255,8 @@
     </row>
     <row r="90" spans="1:12" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
-      <c r="B90" s="61"/>
-      <c r="C90" s="68"/>
+      <c r="B90" s="54"/>
+      <c r="C90" s="61"/>
       <c r="D90" s="13"/>
       <c r="E90" s="18"/>
       <c r="F90" s="18"/>
@@ -8251,37 +8055,6 @@
   <sheetProtection algorithmName="SHA-512" hashValue="jUzRW1wZU4UKDlrc+ZcjfI1CGFMPpb3WBOiNrGujdLz4z6mGk5OrV9Q3LSR9/vcnYNn7Umyfq3hCTh4LwP0m/Q==" saltValue="0LYgXzE3BB0FL5cMFmUsdQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0"/>
   <dataConsolidate/>
   <mergeCells count="43">
-    <mergeCell ref="B83:B90"/>
-    <mergeCell ref="E84:G84"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="C88:C90"/>
-    <mergeCell ref="B75:B82"/>
-    <mergeCell ref="E76:G76"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="C80:C82"/>
-    <mergeCell ref="B47:B70"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="B73:L73"/>
-    <mergeCell ref="B74:L74"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="C58:C60"/>
-    <mergeCell ref="B21:L21"/>
-    <mergeCell ref="B22:L22"/>
-    <mergeCell ref="Q22:Q29"/>
-    <mergeCell ref="B23:B46"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="C37:C38"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="B5:L5"/>
     <mergeCell ref="B6:L6"/>
@@ -8294,19 +8067,97 @@
     <mergeCell ref="E15:G15"/>
     <mergeCell ref="I15:K15"/>
     <mergeCell ref="C16:C18"/>
+    <mergeCell ref="B21:L21"/>
+    <mergeCell ref="B22:L22"/>
+    <mergeCell ref="Q22:Q29"/>
+    <mergeCell ref="B23:B46"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="B47:B70"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="B73:L73"/>
+    <mergeCell ref="B74:L74"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="B75:B82"/>
+    <mergeCell ref="E76:G76"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="C80:C82"/>
+    <mergeCell ref="B83:B90"/>
+    <mergeCell ref="E84:G84"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="C85:C87"/>
+    <mergeCell ref="C88:C90"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <customProperties>
-    <customPr name="IbpWorksheetKeyString_GUID" r:id="rId2"/>
-  </customProperties>
-  <drawing r:id="rId3"/>
-  <legacyDrawing r:id="rId4"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27671" r:id="rId5" name="cbApplyOddEvenFormatting">
-          <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId6">
+        <control shapeId="27649" r:id="rId4" name="cbApplyLevelFormatting">
+          <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>266700</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>66675</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>342900</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="27649" r:id="rId4" name="cbApplyLevelFormatting"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="27655" r:id="rId6" name="cbApplyMemberFormatting">
+          <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId7">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>266700</xdr:colOff>
+                <xdr:row>20</xdr:row>
+                <xdr:rowOff>66675</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>66675</xdr:colOff>
+                <xdr:row>20</xdr:row>
+                <xdr:rowOff>342900</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="27655" r:id="rId6" name="cbApplyMemberFormatting"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="27671" r:id="rId8" name="cbApplyOddEvenFormatting">
+          <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId9">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>1</xdr:col>
@@ -8325,62 +8176,12 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="27671" r:id="rId5" name="cbApplyOddEvenFormatting"/>
+        <control shapeId="27671" r:id="rId8" name="cbApplyOddEvenFormatting"/>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27655" r:id="rId7" name="cbApplyMemberFormatting">
-          <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId8">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>266700</xdr:colOff>
-                <xdr:row>20</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>66675</xdr:colOff>
-                <xdr:row>20</xdr:row>
-                <xdr:rowOff>342900</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="27655" r:id="rId7" name="cbApplyMemberFormatting"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="27649" r:id="rId9" name="cbApplyLevelFormatting">
-          <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" r:id="rId10">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>266700</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>66675</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>66675</xdr:colOff>
-                <xdr:row>4</xdr:row>
-                <xdr:rowOff>342900</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="27649" r:id="rId9" name="cbApplyLevelFormatting"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="27650" r:id="rId11" name="Group Box 2">
+        <control shapeId="27650" r:id="rId10" name="Group Box 2">
           <controlPr defaultSize="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8402,7 +8203,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27651" r:id="rId12" name="obLevelRowFirst">
+        <control shapeId="27651" r:id="rId11" name="obLevelRowFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1">
               <from>
@@ -8424,7 +8225,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27652" r:id="rId13" name="obLevelColumnFirst">
+        <control shapeId="27652" r:id="rId12" name="obLevelColumnFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1">
               <from>
@@ -8446,7 +8247,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27653" r:id="rId14" name="cbUseDefaultLevelFirst">
+        <control shapeId="27653" r:id="rId13" name="cbUseDefaultLevelFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8468,7 +8269,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27654" r:id="rId15" name="cbUseDefaultLevelSecond">
+        <control shapeId="27654" r:id="rId14" name="cbUseDefaultLevelSecond">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8490,7 +8291,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27656" r:id="rId16" name="Group Box 8">
+        <control shapeId="27656" r:id="rId15" name="Group Box 8">
           <controlPr defaultSize="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8512,7 +8313,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27657" r:id="rId17" name="obMemberRowFirst">
+        <control shapeId="27657" r:id="rId16" name="obMemberRowFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1">
               <from>
@@ -8534,7 +8335,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27658" r:id="rId18" name="obMemberColumnFirst">
+        <control shapeId="27658" r:id="rId17" name="obMemberColumnFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1">
               <from>
@@ -8556,7 +8357,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27659" r:id="rId19" name="cbApplyCalculatedMemberFirst">
+        <control shapeId="27659" r:id="rId18" name="cbApplyCalculatedMemberFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8578,7 +8379,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27660" r:id="rId20" name="cbApplyImputableMemberFirst">
+        <control shapeId="27660" r:id="rId19" name="cbApplyImputableMemberFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8600,7 +8401,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27661" r:id="rId21" name="cbApplyLocalMemberFirst">
+        <control shapeId="27661" r:id="rId20" name="cbApplyLocalMemberFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8622,7 +8423,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27662" r:id="rId22" name="cbApplyChangedMemberFirst">
+        <control shapeId="27662" r:id="rId21" name="cbApplyChangedMemberFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8644,7 +8445,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27663" r:id="rId23" name="cbApplySpecificMemberFirst">
+        <control shapeId="27663" r:id="rId22" name="cbApplySpecificMemberFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8666,7 +8467,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27664" r:id="rId24" name="AddMemberFirst">
+        <control shapeId="27664" r:id="rId23" name="AddMemberFirst">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -8688,7 +8489,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27665" r:id="rId25" name="cbApplyCalculatedMemberSecond">
+        <control shapeId="27665" r:id="rId24" name="cbApplyCalculatedMemberSecond">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8710,7 +8511,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27666" r:id="rId26" name="cbApplyImputableMemberSecond">
+        <control shapeId="27666" r:id="rId25" name="cbApplyImputableMemberSecond">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8732,7 +8533,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27667" r:id="rId27" name="cbApplyLocalMemberSecond">
+        <control shapeId="27667" r:id="rId26" name="cbApplyLocalMemberSecond">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8754,7 +8555,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27668" r:id="rId28" name="cbApplyChangedMemberSecond">
+        <control shapeId="27668" r:id="rId27" name="cbApplyChangedMemberSecond">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8776,7 +8577,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27669" r:id="rId29" name="cbApplySpecificMemberSecond">
+        <control shapeId="27669" r:id="rId28" name="cbApplySpecificMemberSecond">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8798,7 +8599,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27670" r:id="rId30" name="AddMemberSecond">
+        <control shapeId="27670" r:id="rId29" name="AddMemberSecond">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -8820,7 +8621,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27672" r:id="rId31" name="Group Box 24">
+        <control shapeId="27672" r:id="rId30" name="Group Box 24">
           <controlPr defaultSize="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8842,7 +8643,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27673" r:id="rId32" name="obOddEvenRowFirst">
+        <control shapeId="27673" r:id="rId31" name="obOddEvenRowFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1">
               <from>
@@ -8864,7 +8665,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27674" r:id="rId33" name="obOddEvenColumnFirst">
+        <control shapeId="27674" r:id="rId32" name="obOddEvenColumnFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1">
               <from>
@@ -8886,7 +8687,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27675" r:id="rId34" name="cbUseOddFirst">
+        <control shapeId="27675" r:id="rId33" name="cbUseOddFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8908,7 +8709,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27676" r:id="rId35" name="cbUseEvenFirst">
+        <control shapeId="27676" r:id="rId34" name="cbUseEvenFirst">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8930,7 +8731,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27677" r:id="rId36" name="cbUseOddSecond">
+        <control shapeId="27677" r:id="rId35" name="cbUseOddSecond">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8952,7 +8753,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27678" r:id="rId37" name="cbUseEvenSecond">
+        <control shapeId="27678" r:id="rId36" name="cbUseEvenSecond">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -8974,7 +8775,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27679" r:id="rId38" name="AddedMember1_1">
+        <control shapeId="27679" r:id="rId37" name="AddedMember1_1">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -8996,7 +8797,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27680" r:id="rId39" name="ChangeMember1_1">
+        <control shapeId="27680" r:id="rId38" name="ChangeMember1_1">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9018,7 +8819,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27681" r:id="rId40" name="UpMember1_1">
+        <control shapeId="27681" r:id="rId39" name="UpMember1_1">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9040,7 +8841,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27682" r:id="rId41" name="DownMember1_1">
+        <control shapeId="27682" r:id="rId40" name="DownMember1_1">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9062,7 +8863,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27683" r:id="rId42" name="AddedMember1_2">
+        <control shapeId="27683" r:id="rId41" name="AddedMember1_2">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9084,7 +8885,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27684" r:id="rId43" name="ChangeMember1_2">
+        <control shapeId="27684" r:id="rId42" name="ChangeMember1_2">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9106,7 +8907,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27685" r:id="rId44" name="UpMember1_2">
+        <control shapeId="27685" r:id="rId43" name="UpMember1_2">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9128,7 +8929,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27686" r:id="rId45" name="DownMember1_2">
+        <control shapeId="27686" r:id="rId44" name="DownMember1_2">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9150,7 +8951,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27687" r:id="rId46" name="AddedMember2_1">
+        <control shapeId="27687" r:id="rId45" name="AddedMember2_1">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9172,7 +8973,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27688" r:id="rId47" name="ChangeMember2_1">
+        <control shapeId="27688" r:id="rId46" name="ChangeMember2_1">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9194,7 +8995,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27689" r:id="rId48" name="UpMember2_1">
+        <control shapeId="27689" r:id="rId47" name="UpMember2_1">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9216,7 +9017,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27690" r:id="rId49" name="DownMember2_1">
+        <control shapeId="27690" r:id="rId48" name="DownMember2_1">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9238,7 +9039,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27691" r:id="rId50" name="AddedMember2_2">
+        <control shapeId="27691" r:id="rId49" name="AddedMember2_2">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9260,7 +9061,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27692" r:id="rId51" name="ChangeMember2_2">
+        <control shapeId="27692" r:id="rId50" name="ChangeMember2_2">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9282,7 +9083,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27693" r:id="rId52" name="UpMember2_2">
+        <control shapeId="27693" r:id="rId51" name="UpMember2_2">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9304,7 +9105,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27694" r:id="rId53" name="DownMember2_2">
+        <control shapeId="27694" r:id="rId52" name="DownMember2_2">
           <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="_xll.IBPXLClient.TechnicalCategory.ButtonActionInIBPClientFormattingSheet">
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
@@ -9326,7 +9127,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27695" r:id="rId54" name="cbApplyLevelFormattingShape">
+        <control shapeId="27695" r:id="rId53" name="cbApplyLevelFormattingShape">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -9348,7 +9149,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27696" r:id="rId55" name="cbApplyMemberFormattingShape">
+        <control shapeId="27696" r:id="rId54" name="cbApplyMemberFormattingShape">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -9370,7 +9171,7 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="27697" r:id="rId56" name="cbApplyOddEvenFormattingShape">
+        <control shapeId="27697" r:id="rId55" name="cbApplyOddEvenFormattingShape">
           <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
             <anchor moveWithCells="1">
               <from>
@@ -9395,7 +9196,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9528,43 +9329,14 @@
   <pageSetup orientation="portrait" horizontalDpi="300" r:id="rId1"/>
   <customProperties>
     <customPr name="EpmWorksheetKeyString_GUID" r:id="rId2"/>
-    <customPr name="IbpWorksheetKeyString_GUID" r:id="rId3"/>
   </customProperties>
-  <drawing r:id="rId4"/>
-  <legacyDrawing r:id="rId5"/>
-  <picture r:id="rId6"/>
-  <controls>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="3093" r:id="rId7" name="FPMExcelClientSheetOptionstb1">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId8">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="3093" r:id="rId7" name="FPMExcelClientSheetOptionstb1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-  </controls>
+  <drawing r:id="rId3"/>
+  <picture r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9699,60 +9471,7 @@
     <customPr name="EpmWorksheetKeyString_GUID" r:id="rId2"/>
   </customProperties>
   <drawing r:id="rId3"/>
-  <legacyDrawing r:id="rId4"/>
-  <picture r:id="rId5"/>
-  <controls>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="5127" r:id="rId6" name="TextBox2">
-          <controlPr defaultSize="0" disabled="1" autoLine="0" r:id="rId7">
-            <anchor>
-              <from>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>76200</xdr:colOff>
-                <xdr:row>5</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>85725</xdr:colOff>
-                <xdr:row>5</xdr:row>
-                <xdr:rowOff>9525</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="5127" r:id="rId6" name="TextBox2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="5121" r:id="rId8" name="FPMExcelClientSheetOptionstb1">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId9">
-            <anchor moveWithCells="1" sizeWithCells="1">
-              <from>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="5121" r:id="rId8" name="FPMExcelClientSheetOptionstb1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-  </controls>
+  <picture r:id="rId4"/>
 </worksheet>
 </file>
 
